--- a/data/raw/Democracy in Action/review/dia_2004_labor_review.xlsx
+++ b/data/raw/Democracy in Action/review/dia_2004_labor_review.xlsx
@@ -9,17 +9,23 @@
     <sheet name="review" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'review'!$A$1:$W$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'review'!$A$1:$Y$79</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="431">
   <si>
     <t xml:space="preserve">row_id</t>
   </si>
   <si>
+    <t xml:space="preserve">review_action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">review_note</t>
+  </si>
+  <si>
     <t xml:space="preserve">contest_id</t>
   </si>
   <si>
@@ -87,6 +93,9 @@
   </si>
   <si>
     <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve">2004D</t>
@@ -1644,28 +1653,30 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="8.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="12.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="17.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="40.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="32.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="21.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="8.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="10.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="20.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="40.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="13.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="18.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="18.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="40.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="11.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="80.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="18.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="20.71" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="40.71" hidden="0" customWidth="1"/>
-    <col min="22" max="22" width="40.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="14.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="40.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="8.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="8.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="17.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="40.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="32.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="21.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="8.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="10.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="20.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="40.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="13.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="18.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="18.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="40.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="11.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="80.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="18.71" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="20.71" hidden="0" customWidth="1"/>
     <col min="23" max="23" width="40.71" hidden="0" customWidth="1"/>
+    <col min="24" max="24" width="40.71" hidden="0" customWidth="1"/>
+    <col min="25" max="25" width="40.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1738,4388 +1749,4862 @@
       <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="X1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J2" s="1"/>
-      <c r="K2" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q2" s="1" t="s">
+      <c r="O2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="M3" s="1"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
+      <c r="O3" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P3" s="1"/>
-      <c r="Q3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
       <c r="S3" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="W3" s="1"/>
+        <v>39</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y3" s="1"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J4" s="1"/>
-      <c r="K4" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>47</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="N4" s="1"/>
       <c r="O4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="P4" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="Q4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>49</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="R4" s="1"/>
       <c r="S4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J5" s="1"/>
-      <c r="K5" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
+      <c r="O5" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P5" s="1"/>
-      <c r="Q5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>55</v>
-      </c>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
       <c r="S5" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>54</v>
+        <v>45</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J6" s="1"/>
-      <c r="K6" s="1" t="s">
-        <v>59</v>
-      </c>
+      <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
+      <c r="O6" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P6" s="1"/>
-      <c r="Q6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>60</v>
-      </c>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
       <c r="S6" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>59</v>
+        <v>45</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J7" s="1"/>
-      <c r="K7" s="1" t="s">
-        <v>64</v>
-      </c>
+      <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
       <c r="R7" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y7" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="W7" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J8" s="1"/>
-      <c r="K8" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
       <c r="R8" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y8" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="W8" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J9" s="1"/>
-      <c r="K9" s="1" t="s">
-        <v>76</v>
-      </c>
+      <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
+      <c r="O9" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P9" s="1"/>
-      <c r="Q9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>77</v>
-      </c>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
       <c r="S9" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>76</v>
+        <v>45</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y9" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J10" s="1"/>
-      <c r="K10" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
       <c r="M10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
+        <v>84</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P10" s="1"/>
-      <c r="Q10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
       <c r="S10" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y10" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J11" s="1"/>
-      <c r="K11" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1" t="s">
-        <v>31</v>
+        <v>90</v>
       </c>
       <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
       <c r="R11" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="U11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y11" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="V11" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="W11" s="1" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J12" s="1"/>
-      <c r="K12" s="1" t="s">
-        <v>94</v>
-      </c>
+      <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>47</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="N12" s="1"/>
       <c r="O12" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="P12" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="Q12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>95</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="R12" s="1"/>
       <c r="S12" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="V12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y12" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="W12" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J13" s="1"/>
-      <c r="K13" s="1" t="s">
-        <v>59</v>
-      </c>
+      <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
+      <c r="O13" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P13" s="1"/>
-      <c r="Q13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R13" s="1" t="s">
-        <v>100</v>
-      </c>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
       <c r="S13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>36</v>
+        <v>103</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>59</v>
+        <v>99</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>104</v>
+        <v>29</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+        <v>106</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J14" s="1"/>
-      <c r="K14" s="1" t="s">
-        <v>105</v>
-      </c>
+      <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1" t="s">
-        <v>31</v>
+        <v>108</v>
       </c>
       <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
       <c r="R14" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T14" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="W14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="X14" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y14" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="U14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="V14" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="W14" s="1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>112</v>
+        <v>29</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+        <v>114</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J15" s="1"/>
-      <c r="K15" s="1" t="s">
-        <v>113</v>
-      </c>
+      <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
       <c r="R15" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>118</v>
+        <v>45</v>
+      </c>
+      <c r="X15" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y15" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="V16" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1" t="s">
+      <c r="W16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="X16" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="L16" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1" t="s">
+      <c r="Y16" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="U16" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="V16" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="W16" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>125</v>
+        <v>29</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
+        <v>114</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J17" s="1"/>
-      <c r="K17" s="1" t="s">
-        <v>113</v>
-      </c>
+      <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q17" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
       <c r="R17" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>129</v>
+        <v>45</v>
+      </c>
+      <c r="X17" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Y17" s="1" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>131</v>
+        <v>29</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
+        <v>114</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J18" s="1"/>
-      <c r="K18" s="1" t="s">
-        <v>132</v>
-      </c>
+      <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1" t="s">
-        <v>31</v>
+        <v>135</v>
       </c>
       <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
+      <c r="O18" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P18" s="1"/>
-      <c r="Q18" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>133</v>
-      </c>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
       <c r="S18" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>132</v>
+        <v>45</v>
+      </c>
+      <c r="X18" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y18" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>136</v>
+        <v>29</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J19" s="1"/>
-      <c r="K19" s="1" t="s">
-        <v>137</v>
-      </c>
+      <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1" t="s">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
+      <c r="O19" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P19" s="1"/>
-      <c r="Q19" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R19" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
       <c r="S19" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V19" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="W19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y19" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="W19" s="1" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J20" s="1"/>
-      <c r="K20" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1" t="s">
-        <v>31</v>
+        <v>146</v>
       </c>
       <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
+      <c r="O20" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P20" s="1"/>
-      <c r="Q20" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R20" s="1" t="s">
-        <v>144</v>
-      </c>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
       <c r="S20" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>143</v>
+        <v>45</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>147</v>
+        <v>29</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J21" s="1"/>
-      <c r="K21" s="1" t="s">
-        <v>148</v>
-      </c>
+      <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1" t="s">
-        <v>31</v>
+        <v>151</v>
       </c>
       <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
+      <c r="O21" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P21" s="1"/>
-      <c r="Q21" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>149</v>
-      </c>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
       <c r="S21" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>148</v>
+        <v>45</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>152</v>
+        <v>29</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J22" s="1"/>
-      <c r="K22" s="1" t="s">
-        <v>153</v>
-      </c>
+      <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1" t="s">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
       <c r="R22" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V22" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="W22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="X22" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y22" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="W22" s="1" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>158</v>
+        <v>29</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
-      <c r="M23" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="M23" s="1"/>
       <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
+      <c r="O23" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P23" s="1"/>
-      <c r="Q23" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>159</v>
-      </c>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
       <c r="S23" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V23" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="W23" s="1"/>
+        <v>142</v>
+      </c>
+      <c r="W23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="X23" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y23" s="1"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>162</v>
+        <v>29</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J24" s="1"/>
-      <c r="K24" s="1" t="s">
-        <v>163</v>
-      </c>
+      <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1" t="s">
-        <v>31</v>
+        <v>166</v>
       </c>
       <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
+      <c r="O24" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P24" s="1"/>
-      <c r="Q24" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R24" s="1" t="s">
-        <v>164</v>
-      </c>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
       <c r="S24" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>163</v>
+        <v>45</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y24" s="1" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
+      <c r="I25" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J25" s="1"/>
-      <c r="K25" s="1" t="s">
-        <v>167</v>
-      </c>
+      <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1" t="s">
-        <v>31</v>
+        <v>170</v>
       </c>
       <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
+      <c r="O25" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P25" s="1"/>
-      <c r="Q25" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R25" s="1" t="s">
-        <v>168</v>
-      </c>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
       <c r="S25" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>139</v>
+        <v>171</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>167</v>
+        <v>45</v>
+      </c>
+      <c r="X25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y25" s="1" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>170</v>
+        <v>29</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J26" s="1"/>
-      <c r="K26" s="1" t="s">
-        <v>171</v>
-      </c>
+      <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1" t="s">
-        <v>31</v>
+        <v>174</v>
       </c>
       <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
+      <c r="O26" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P26" s="1"/>
-      <c r="Q26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R26" s="1" t="s">
-        <v>172</v>
-      </c>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
       <c r="S26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>171</v>
+        <v>45</v>
+      </c>
+      <c r="X26" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="Y26" s="1" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>175</v>
+        <v>29</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J27" s="1"/>
-      <c r="K27" s="1" t="s">
-        <v>176</v>
-      </c>
+      <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1" t="s">
-        <v>31</v>
+        <v>179</v>
       </c>
       <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
+      <c r="O27" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P27" s="1"/>
-      <c r="Q27" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R27" s="1" t="s">
-        <v>177</v>
-      </c>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
       <c r="S27" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V27" s="1" t="s">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>176</v>
+        <v>45</v>
+      </c>
+      <c r="X27" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y27" s="1" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>180</v>
+        <v>29</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J28" s="1"/>
-      <c r="K28" s="1" t="s">
-        <v>181</v>
-      </c>
+      <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1" t="s">
-        <v>31</v>
+        <v>184</v>
       </c>
       <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
+      <c r="O28" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P28" s="1"/>
-      <c r="Q28" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R28" s="1" t="s">
-        <v>182</v>
-      </c>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
       <c r="S28" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>139</v>
+        <v>185</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V28" s="1" t="s">
-        <v>183</v>
+        <v>142</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>181</v>
+        <v>45</v>
+      </c>
+      <c r="X28" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="Y28" s="1" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>185</v>
+        <v>29</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J29" s="1"/>
-      <c r="K29" s="1" t="s">
-        <v>186</v>
-      </c>
+      <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1" t="s">
-        <v>31</v>
+        <v>189</v>
       </c>
       <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
+      <c r="O29" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P29" s="1"/>
-      <c r="Q29" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R29" s="1" t="s">
-        <v>187</v>
-      </c>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
       <c r="S29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="U29" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>186</v>
+        <v>45</v>
+      </c>
+      <c r="X29" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y29" s="1" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>190</v>
+        <v>29</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J30" s="1"/>
-      <c r="K30" s="1" t="s">
-        <v>191</v>
-      </c>
+      <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1" t="s">
-        <v>31</v>
+        <v>194</v>
       </c>
       <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
+      <c r="O30" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P30" s="1"/>
-      <c r="Q30" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R30" s="1" t="s">
-        <v>192</v>
-      </c>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1"/>
       <c r="S30" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V30" s="1" t="s">
-        <v>193</v>
+        <v>142</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>191</v>
+        <v>45</v>
+      </c>
+      <c r="X30" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y30" s="1" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>195</v>
+        <v>29</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J31" s="1"/>
-      <c r="K31" s="1" t="s">
-        <v>196</v>
-      </c>
+      <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1" t="s">
-        <v>31</v>
+        <v>199</v>
       </c>
       <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
+      <c r="O31" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P31" s="1"/>
-      <c r="Q31" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R31" s="1" t="s">
-        <v>197</v>
-      </c>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
       <c r="S31" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>139</v>
+        <v>200</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V31" s="1" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>196</v>
+        <v>45</v>
+      </c>
+      <c r="X31" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y31" s="1" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>200</v>
+        <v>29</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J32" s="1"/>
-      <c r="K32" s="1" t="s">
-        <v>201</v>
-      </c>
+      <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1" t="s">
-        <v>31</v>
+        <v>204</v>
       </c>
       <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q32" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O32" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
       <c r="R32" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="S32" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>139</v>
+        <v>206</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V32" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="W32" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="X32" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y32" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="W32" s="1" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>206</v>
+        <v>29</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J33" s="1"/>
-      <c r="K33" s="1" t="s">
-        <v>207</v>
-      </c>
+      <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1" t="s">
-        <v>31</v>
+        <v>210</v>
       </c>
       <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q33" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O33" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
       <c r="R33" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>139</v>
+        <v>212</v>
       </c>
       <c r="U33" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V33" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="W33" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="X33" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="Y33" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="W33" s="1" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>212</v>
+        <v>29</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J34" s="1"/>
-      <c r="K34" s="1" t="s">
-        <v>213</v>
-      </c>
+      <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1" t="s">
-        <v>31</v>
+        <v>216</v>
       </c>
       <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q34" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
       <c r="R34" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>139</v>
+        <v>218</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V34" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="W34" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="X34" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="Y34" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="W34" s="1" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>218</v>
+        <v>29</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J35" s="1"/>
-      <c r="K35" s="1" t="s">
-        <v>219</v>
-      </c>
+      <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1" t="s">
-        <v>31</v>
+        <v>222</v>
       </c>
       <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="Q35" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="1"/>
       <c r="R35" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>139</v>
+        <v>224</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V35" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="W35" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="X35" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y35" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="W35" s="1" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>224</v>
+        <v>29</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J36" s="1"/>
-      <c r="K36" s="1" t="s">
-        <v>225</v>
-      </c>
+      <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1" t="s">
-        <v>31</v>
+        <v>228</v>
       </c>
       <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-      <c r="P36" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q36" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P36" s="1"/>
+      <c r="Q36" s="1"/>
       <c r="R36" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="S36" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>139</v>
+        <v>230</v>
       </c>
       <c r="U36" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V36" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="W36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="X36" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="Y36" s="1" t="s">
         <v>228</v>
-      </c>
-      <c r="W36" s="1" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>230</v>
+        <v>29</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J37" s="1"/>
-      <c r="K37" s="1" t="s">
-        <v>231</v>
-      </c>
+      <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1" t="s">
-        <v>31</v>
+        <v>234</v>
       </c>
       <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="Q37" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O37" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P37" s="1"/>
+      <c r="Q37" s="1"/>
       <c r="R37" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>139</v>
+        <v>236</v>
       </c>
       <c r="U37" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V37" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="W37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="X37" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="Y37" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="W37" s="1" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>236</v>
+        <v>29</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J38" s="1"/>
-      <c r="K38" s="1" t="s">
-        <v>237</v>
-      </c>
+      <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q38" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O38" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="1"/>
       <c r="R38" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="S38" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>139</v>
+        <v>242</v>
       </c>
       <c r="U38" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="V38" s="1" t="s">
-        <v>240</v>
+        <v>142</v>
       </c>
       <c r="W38" s="1" t="s">
-        <v>241</v>
+        <v>45</v>
+      </c>
+      <c r="X38" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="Y38" s="1" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>243</v>
+        <v>29</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J39" s="1"/>
-      <c r="K39" s="1" t="s">
-        <v>196</v>
-      </c>
+      <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1" t="s">
-        <v>31</v>
+        <v>199</v>
       </c>
       <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
+      <c r="O39" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P39" s="1"/>
-      <c r="Q39" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R39" s="1" t="s">
-        <v>244</v>
-      </c>
+      <c r="Q39" s="1"/>
+      <c r="R39" s="1"/>
       <c r="S39" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>139</v>
+        <v>247</v>
       </c>
       <c r="U39" s="1" t="s">
-        <v>245</v>
+        <v>38</v>
       </c>
       <c r="V39" s="1" t="s">
-        <v>246</v>
+        <v>142</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>196</v>
+        <v>248</v>
+      </c>
+      <c r="X39" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="Y39" s="1" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>248</v>
+        <v>28</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>249</v>
+        <v>29</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
+        <v>251</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J40" s="1"/>
-      <c r="K40" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>252</v>
-      </c>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
       <c r="M40" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
+        <v>254</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P40" s="1"/>
-      <c r="Q40" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R40" s="1" t="s">
-        <v>253</v>
-      </c>
+      <c r="Q40" s="1"/>
+      <c r="R40" s="1"/>
       <c r="S40" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T40" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="U40" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V40" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="W40" s="1"/>
+      <c r="X40" s="1"/>
+      <c r="Y40" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="T40" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="U40" s="1"/>
-      <c r="V40" s="1"/>
-      <c r="W40" s="1" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="F41" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P41" s="1"/>
+      <c r="Q41" s="1"/>
+      <c r="R41" s="1"/>
+      <c r="S41" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T41" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="U41" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="G41" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="M41" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="P41" s="1"/>
-      <c r="Q41" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R41" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="S41" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="T41" s="1" t="s">
+      <c r="V41" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="W41" s="1"/>
+      <c r="X41" s="1"/>
+      <c r="Y41" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="U41" s="1"/>
-      <c r="V41" s="1"/>
-      <c r="W41" s="1" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>263</v>
+        <v>29</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
+        <v>114</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J42" s="1"/>
-      <c r="K42" s="1" t="s">
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P42" s="1"/>
+      <c r="Q42" s="1"/>
+      <c r="R42" s="1"/>
+      <c r="S42" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T42" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="U42" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V42" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="L42" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="M42" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
-      <c r="P42" s="1"/>
-      <c r="Q42" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R42" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="S42" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="T42" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="U42" s="1"/>
-      <c r="V42" s="1"/>
-      <c r="W42" s="1" t="s">
-        <v>264</v>
+      <c r="W42" s="1"/>
+      <c r="X42" s="1"/>
+      <c r="Y42" s="1" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>268</v>
+        <v>29</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
+        <v>114</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J43" s="1"/>
-      <c r="K43" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>270</v>
-      </c>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
       <c r="M43" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
+        <v>272</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P43" s="1"/>
-      <c r="Q43" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R43" s="1" t="s">
-        <v>271</v>
-      </c>
+      <c r="Q43" s="1"/>
+      <c r="R43" s="1"/>
       <c r="S43" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="U43" s="1"/>
-      <c r="V43" s="1"/>
-      <c r="W43" s="1" t="s">
-        <v>269</v>
+        <v>274</v>
+      </c>
+      <c r="U43" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V43" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="W43" s="1"/>
+      <c r="X43" s="1"/>
+      <c r="Y43" s="1" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>273</v>
+        <v>29</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
+        <v>114</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J44" s="1"/>
-      <c r="K44" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>275</v>
-      </c>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
       <c r="M44" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-      <c r="P44" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="Q44" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P44" s="1"/>
+      <c r="Q44" s="1"/>
       <c r="R44" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="S44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T44" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="U44" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V44" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="W44" s="1"/>
+      <c r="X44" s="1"/>
+      <c r="Y44" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="S44" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="T44" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="U44" s="1"/>
-      <c r="V44" s="1"/>
-      <c r="W44" s="1" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>279</v>
+        <v>29</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
+        <v>114</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J45" s="1"/>
-      <c r="K45" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="L45" s="1" t="s">
-        <v>281</v>
-      </c>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
       <c r="M45" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
-      <c r="P45" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q45" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P45" s="1"/>
+      <c r="Q45" s="1"/>
       <c r="R45" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="S45" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T45" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="U45" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V45" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="W45" s="1"/>
+      <c r="X45" s="1"/>
+      <c r="Y45" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="S45" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="T45" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="U45" s="1"/>
-      <c r="V45" s="1"/>
-      <c r="W45" s="1" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>285</v>
+        <v>29</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
+        <v>114</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J46" s="1"/>
-      <c r="K46" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>287</v>
-      </c>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
       <c r="M46" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
+        <v>289</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P46" s="1"/>
-      <c r="Q46" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R46" s="1" t="s">
-        <v>288</v>
-      </c>
+      <c r="Q46" s="1"/>
+      <c r="R46" s="1"/>
       <c r="S46" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="U46" s="1"/>
-      <c r="V46" s="1"/>
-      <c r="W46" s="1" t="s">
-        <v>286</v>
+        <v>291</v>
+      </c>
+      <c r="U46" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V46" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="W46" s="1"/>
+      <c r="X46" s="1"/>
+      <c r="Y46" s="1" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>290</v>
+        <v>29</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
+        <v>106</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J47" s="1"/>
-      <c r="K47" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="L47" s="1" t="s">
-        <v>292</v>
-      </c>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
       <c r="M47" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
+        <v>294</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P47" s="1"/>
-      <c r="Q47" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R47" s="1" t="s">
-        <v>293</v>
-      </c>
+      <c r="Q47" s="1"/>
+      <c r="R47" s="1"/>
       <c r="S47" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T47" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="U47" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V47" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="W47" s="1"/>
+      <c r="X47" s="1"/>
+      <c r="Y47" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="U47" s="1"/>
-      <c r="V47" s="1"/>
-      <c r="W47" s="1" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>296</v>
+        <v>29</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
+        <v>106</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J48" s="1"/>
-      <c r="K48" s="1" t="s">
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P48" s="1"/>
+      <c r="Q48" s="1"/>
+      <c r="R48" s="1"/>
+      <c r="S48" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T48" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="U48" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V48" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="L48" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="M48" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
-      <c r="P48" s="1"/>
-      <c r="Q48" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R48" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="S48" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="T48" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="U48" s="1"/>
-      <c r="V48" s="1"/>
-      <c r="W48" s="1" t="s">
-        <v>297</v>
+      <c r="W48" s="1"/>
+      <c r="X48" s="1"/>
+      <c r="Y48" s="1" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>301</v>
+        <v>29</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
+        <v>106</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
-      <c r="L49" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="M49" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N49" s="1"/>
-      <c r="O49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P49" s="1"/>
-      <c r="Q49" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R49" s="1" t="s">
-        <v>301</v>
-      </c>
+      <c r="Q49" s="1"/>
+      <c r="R49" s="1"/>
       <c r="S49" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="U49" s="1"/>
-      <c r="V49" s="1"/>
+        <v>304</v>
+      </c>
+      <c r="U49" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V49" s="1" t="s">
+        <v>297</v>
+      </c>
       <c r="W49" s="1"/>
+      <c r="X49" s="1"/>
+      <c r="Y49" s="1"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>304</v>
+        <v>29</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J50" s="1"/>
-      <c r="K50" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="L50" s="1" t="s">
-        <v>305</v>
-      </c>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
       <c r="M50" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N50" s="1"/>
-      <c r="O50" s="1"/>
+        <v>272</v>
+      </c>
+      <c r="N50" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P50" s="1"/>
-      <c r="Q50" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R50" s="1" t="s">
-        <v>306</v>
-      </c>
+      <c r="Q50" s="1"/>
+      <c r="R50" s="1"/>
       <c r="S50" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="U50" s="1"/>
-      <c r="V50" s="1"/>
-      <c r="W50" s="1" t="s">
-        <v>269</v>
+        <v>309</v>
+      </c>
+      <c r="U50" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V50" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="W50" s="1"/>
+      <c r="X50" s="1"/>
+      <c r="Y50" s="1" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>309</v>
+        <v>29</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J51" s="1"/>
-      <c r="K51" s="1" t="s">
-        <v>310</v>
-      </c>
+      <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1" t="s">
-        <v>31</v>
+        <v>313</v>
       </c>
       <c r="N51" s="1"/>
-      <c r="O51" s="1"/>
+      <c r="O51" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P51" s="1"/>
-      <c r="Q51" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R51" s="1" t="s">
-        <v>311</v>
-      </c>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1"/>
       <c r="S51" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="U51" s="1"/>
-      <c r="V51" s="1"/>
-      <c r="W51" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="U51" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V51" s="1" t="s">
         <v>310</v>
+      </c>
+      <c r="W51" s="1"/>
+      <c r="X51" s="1"/>
+      <c r="Y51" s="1" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>313</v>
+        <v>29</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J52" s="1"/>
-      <c r="K52" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="L52" s="1" t="s">
-        <v>315</v>
-      </c>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
       <c r="M52" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N52" s="1"/>
-      <c r="O52" s="1"/>
+        <v>317</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P52" s="1"/>
-      <c r="Q52" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R52" s="1" t="s">
-        <v>316</v>
-      </c>
+      <c r="Q52" s="1"/>
+      <c r="R52" s="1"/>
       <c r="S52" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="U52" s="1"/>
-      <c r="V52" s="1"/>
-      <c r="W52" s="1" t="s">
-        <v>314</v>
+        <v>319</v>
+      </c>
+      <c r="U52" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V52" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="W52" s="1"/>
+      <c r="X52" s="1"/>
+      <c r="Y52" s="1" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>318</v>
+        <v>29</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J53" s="1"/>
-      <c r="K53" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>319</v>
-      </c>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
       <c r="M53" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N53" s="1"/>
-      <c r="O53" s="1"/>
+        <v>300</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P53" s="1"/>
-      <c r="Q53" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R53" s="1" t="s">
-        <v>320</v>
-      </c>
+      <c r="Q53" s="1"/>
+      <c r="R53" s="1"/>
       <c r="S53" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="U53" s="1"/>
-      <c r="V53" s="1"/>
-      <c r="W53" s="1" t="s">
-        <v>297</v>
+        <v>323</v>
+      </c>
+      <c r="U53" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V53" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="W53" s="1"/>
+      <c r="X53" s="1"/>
+      <c r="Y53" s="1" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>322</v>
+        <v>29</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J54" s="1"/>
-      <c r="K54" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="L54" s="1" t="s">
-        <v>324</v>
-      </c>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
       <c r="M54" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
+        <v>326</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P54" s="1"/>
-      <c r="Q54" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R54" s="1" t="s">
-        <v>325</v>
-      </c>
+      <c r="Q54" s="1"/>
+      <c r="R54" s="1"/>
       <c r="S54" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="U54" s="1"/>
-      <c r="V54" s="1"/>
-      <c r="W54" s="1" t="s">
-        <v>323</v>
+        <v>328</v>
+      </c>
+      <c r="U54" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V54" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="W54" s="1"/>
+      <c r="X54" s="1"/>
+      <c r="Y54" s="1" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>327</v>
+        <v>29</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J55" s="1"/>
-      <c r="K55" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="L55" s="1" t="s">
-        <v>329</v>
-      </c>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
       <c r="M55" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N55" s="1"/>
-      <c r="O55" s="1"/>
+        <v>331</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P55" s="1"/>
-      <c r="Q55" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R55" s="1" t="s">
-        <v>330</v>
-      </c>
+      <c r="Q55" s="1"/>
+      <c r="R55" s="1"/>
       <c r="S55" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="U55" s="1"/>
-      <c r="V55" s="1"/>
-      <c r="W55" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
+      </c>
+      <c r="U55" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V55" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="W55" s="1"/>
+      <c r="X55" s="1"/>
+      <c r="Y55" s="1" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>332</v>
+        <v>29</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J56" s="1"/>
-      <c r="K56" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="L56" s="1" t="s">
-        <v>334</v>
-      </c>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
       <c r="M56" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N56" s="1"/>
-      <c r="O56" s="1"/>
+        <v>336</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P56" s="1"/>
-      <c r="Q56" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R56" s="1" t="s">
-        <v>335</v>
-      </c>
+      <c r="Q56" s="1"/>
+      <c r="R56" s="1"/>
       <c r="S56" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="U56" s="1"/>
-      <c r="V56" s="1"/>
-      <c r="W56" s="1" t="s">
-        <v>333</v>
+        <v>338</v>
+      </c>
+      <c r="U56" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V56" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="W56" s="1"/>
+      <c r="X56" s="1"/>
+      <c r="Y56" s="1" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>337</v>
+        <v>29</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J57" s="1"/>
-      <c r="K57" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="L57" s="1" t="s">
-        <v>339</v>
-      </c>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
       <c r="M57" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
+        <v>341</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P57" s="1"/>
-      <c r="Q57" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R57" s="1" t="s">
-        <v>340</v>
-      </c>
+      <c r="Q57" s="1"/>
+      <c r="R57" s="1"/>
       <c r="S57" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="U57" s="1"/>
-      <c r="V57" s="1"/>
-      <c r="W57" s="1" t="s">
-        <v>338</v>
+        <v>343</v>
+      </c>
+      <c r="U57" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V57" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="W57" s="1"/>
+      <c r="X57" s="1"/>
+      <c r="Y57" s="1" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>342</v>
+        <v>29</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J58" s="1"/>
-      <c r="K58" s="1" t="s">
-        <v>343</v>
-      </c>
+      <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1" t="s">
-        <v>31</v>
+        <v>346</v>
       </c>
       <c r="N58" s="1"/>
-      <c r="O58" s="1"/>
+      <c r="O58" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P58" s="1"/>
-      <c r="Q58" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R58" s="1" t="s">
-        <v>344</v>
-      </c>
+      <c r="Q58" s="1"/>
+      <c r="R58" s="1"/>
       <c r="S58" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="U58" s="1"/>
-      <c r="V58" s="1"/>
-      <c r="W58" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
+      </c>
+      <c r="U58" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V58" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="W58" s="1"/>
+      <c r="X58" s="1"/>
+      <c r="Y58" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>346</v>
+        <v>29</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J59" s="1"/>
-      <c r="K59" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="L59" s="1" t="s">
-        <v>348</v>
-      </c>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
       <c r="M59" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N59" s="1"/>
-      <c r="O59" s="1"/>
+        <v>350</v>
+      </c>
+      <c r="N59" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="O59" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P59" s="1"/>
-      <c r="Q59" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R59" s="1" t="s">
-        <v>349</v>
-      </c>
+      <c r="Q59" s="1"/>
+      <c r="R59" s="1"/>
       <c r="S59" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="U59" s="1"/>
-      <c r="V59" s="1"/>
-      <c r="W59" s="1" t="s">
-        <v>347</v>
+        <v>352</v>
+      </c>
+      <c r="U59" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V59" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="W59" s="1"/>
+      <c r="X59" s="1"/>
+      <c r="Y59" s="1" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>351</v>
+        <v>29</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J60" s="1"/>
-      <c r="K60" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="L60" s="1" t="s">
-        <v>353</v>
-      </c>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
       <c r="M60" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
+        <v>355</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P60" s="1"/>
-      <c r="Q60" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R60" s="1" t="s">
-        <v>354</v>
-      </c>
+      <c r="Q60" s="1"/>
+      <c r="R60" s="1"/>
       <c r="S60" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="U60" s="1"/>
-      <c r="V60" s="1"/>
-      <c r="W60" s="1" t="s">
-        <v>352</v>
+        <v>357</v>
+      </c>
+      <c r="U60" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V60" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="W60" s="1"/>
+      <c r="X60" s="1"/>
+      <c r="Y60" s="1" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>356</v>
+        <v>29</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J61" s="1"/>
-      <c r="K61" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>358</v>
-      </c>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
       <c r="M61" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N61" s="1"/>
-      <c r="O61" s="1"/>
+        <v>360</v>
+      </c>
+      <c r="N61" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P61" s="1"/>
-      <c r="Q61" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R61" s="1" t="s">
-        <v>359</v>
-      </c>
+      <c r="Q61" s="1"/>
+      <c r="R61" s="1"/>
       <c r="S61" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="U61" s="1"/>
-      <c r="V61" s="1"/>
-      <c r="W61" s="1" t="s">
-        <v>357</v>
+        <v>362</v>
+      </c>
+      <c r="U61" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V61" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="W61" s="1"/>
+      <c r="X61" s="1"/>
+      <c r="Y61" s="1" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>361</v>
+        <v>29</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
-      <c r="M62" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="M62" s="1"/>
       <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
+      <c r="O62" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P62" s="1"/>
-      <c r="Q62" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R62" s="1" t="s">
-        <v>361</v>
-      </c>
+      <c r="Q62" s="1"/>
+      <c r="R62" s="1"/>
       <c r="S62" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="U62" s="1"/>
-      <c r="V62" s="1"/>
+        <v>364</v>
+      </c>
+      <c r="U62" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V62" s="1" t="s">
+        <v>310</v>
+      </c>
       <c r="W62" s="1"/>
+      <c r="X62" s="1"/>
+      <c r="Y62" s="1"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>363</v>
+        <v>29</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J63" s="1"/>
-      <c r="K63" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="L63" s="1" t="s">
-        <v>365</v>
-      </c>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
       <c r="M63" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N63" s="1"/>
-      <c r="O63" s="1"/>
-      <c r="P63" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="Q63" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="N63" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P63" s="1"/>
+      <c r="Q63" s="1"/>
       <c r="R63" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="S63" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T63" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="U63" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V63" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="W63" s="1"/>
+      <c r="X63" s="1"/>
+      <c r="Y63" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="S63" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="T63" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="U63" s="1"/>
-      <c r="V63" s="1"/>
-      <c r="W63" s="1" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>370</v>
+        <v>29</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J64" s="1"/>
-      <c r="K64" s="1" t="s">
+      <c r="K64" s="1"/>
+      <c r="L64" s="1"/>
+      <c r="M64" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="N64" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P64" s="1"/>
+      <c r="Q64" s="1"/>
+      <c r="R64" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="S64" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T64" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="U64" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V64" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="L64" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="M64" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N64" s="1"/>
-      <c r="O64" s="1"/>
-      <c r="P64" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="Q64" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R64" s="1" t="s">
+      <c r="W64" s="1"/>
+      <c r="X64" s="1"/>
+      <c r="Y64" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="S64" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="T64" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="U64" s="1"/>
-      <c r="V64" s="1"/>
-      <c r="W64" s="1" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>376</v>
+        <v>29</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
-      <c r="L65" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="M65" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N65" s="1"/>
-      <c r="O65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
+      <c r="N65" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P65" s="1"/>
-      <c r="Q65" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R65" s="1" t="s">
-        <v>378</v>
-      </c>
+      <c r="Q65" s="1"/>
+      <c r="R65" s="1"/>
       <c r="S65" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="U65" s="1"/>
-      <c r="V65" s="1"/>
+        <v>381</v>
+      </c>
+      <c r="U65" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V65" s="1" t="s">
+        <v>371</v>
+      </c>
       <c r="W65" s="1"/>
+      <c r="X65" s="1"/>
+      <c r="Y65" s="1"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>380</v>
+        <v>29</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
-      <c r="L66" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="M66" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N66" s="1"/>
-      <c r="O66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1"/>
+      <c r="N66" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P66" s="1"/>
-      <c r="Q66" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R66" s="1" t="s">
-        <v>378</v>
-      </c>
+      <c r="Q66" s="1"/>
+      <c r="R66" s="1"/>
       <c r="S66" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="U66" s="1"/>
-      <c r="V66" s="1"/>
+        <v>381</v>
+      </c>
+      <c r="U66" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V66" s="1" t="s">
+        <v>371</v>
+      </c>
       <c r="W66" s="1"/>
+      <c r="X66" s="1"/>
+      <c r="Y66" s="1"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>382</v>
+        <v>29</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
-      <c r="L67" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="M67" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N67" s="1"/>
-      <c r="O67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1"/>
+      <c r="N67" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P67" s="1"/>
-      <c r="Q67" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R67" s="1" t="s">
-        <v>378</v>
-      </c>
+      <c r="Q67" s="1"/>
+      <c r="R67" s="1"/>
       <c r="S67" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="U67" s="1"/>
-      <c r="V67" s="1"/>
+        <v>381</v>
+      </c>
+      <c r="U67" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V67" s="1" t="s">
+        <v>371</v>
+      </c>
       <c r="W67" s="1"/>
+      <c r="X67" s="1"/>
+      <c r="Y67" s="1"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>384</v>
+        <v>29</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J68" s="1"/>
-      <c r="K68" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="L68" s="1" t="s">
-        <v>386</v>
-      </c>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
       <c r="M68" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N68" s="1"/>
-      <c r="O68" s="1"/>
-      <c r="P68" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="Q68" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P68" s="1"/>
+      <c r="Q68" s="1"/>
       <c r="R68" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="S68" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T68" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="U68" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V68" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="W68" s="1"/>
+      <c r="X68" s="1"/>
+      <c r="Y68" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="S68" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="T68" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="U68" s="1"/>
-      <c r="V68" s="1"/>
-      <c r="W68" s="1" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>390</v>
+        <v>29</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J69" s="1"/>
-      <c r="K69" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>392</v>
-      </c>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
       <c r="M69" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N69" s="1"/>
-      <c r="O69" s="1"/>
-      <c r="P69" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="Q69" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="N69" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P69" s="1"/>
+      <c r="Q69" s="1"/>
       <c r="R69" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="S69" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T69" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="U69" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V69" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="W69" s="1"/>
+      <c r="X69" s="1"/>
+      <c r="Y69" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="S69" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="T69" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="U69" s="1"/>
-      <c r="V69" s="1"/>
-      <c r="W69" s="1" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>396</v>
+        <v>29</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J70" s="1"/>
-      <c r="K70" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="L70" s="1" t="s">
-        <v>398</v>
-      </c>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
       <c r="M70" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N70" s="1"/>
-      <c r="O70" s="1"/>
-      <c r="P70" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="Q70" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="N70" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P70" s="1"/>
+      <c r="Q70" s="1"/>
       <c r="R70" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="S70" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T70" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="U70" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V70" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="W70" s="1"/>
+      <c r="X70" s="1"/>
+      <c r="Y70" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="S70" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="T70" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="U70" s="1"/>
-      <c r="V70" s="1"/>
-      <c r="W70" s="1" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>402</v>
+        <v>28</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>403</v>
+        <v>29</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
+        <v>405</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J71" s="1"/>
-      <c r="K71" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="L71" s="1" t="s">
-        <v>405</v>
-      </c>
+      <c r="K71" s="1"/>
+      <c r="L71" s="1"/>
       <c r="M71" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N71" s="1"/>
-      <c r="O71" s="1"/>
+        <v>407</v>
+      </c>
+      <c r="N71" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P71" s="1"/>
-      <c r="Q71" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R71" s="1" t="s">
-        <v>406</v>
-      </c>
+      <c r="Q71" s="1"/>
+      <c r="R71" s="1"/>
       <c r="S71" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T71" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="U71" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V71" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="W71" s="1"/>
+      <c r="X71" s="1"/>
+      <c r="Y71" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="U71" s="1"/>
-      <c r="V71" s="1"/>
-      <c r="W71" s="1" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>409</v>
+        <v>28</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>410</v>
+        <v>29</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
+        <v>412</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J72" s="1"/>
-      <c r="K72" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="L72" s="1" t="s">
-        <v>412</v>
-      </c>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
       <c r="M72" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N72" s="1"/>
-      <c r="O72" s="1"/>
+        <v>414</v>
+      </c>
+      <c r="N72" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="O72" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P72" s="1"/>
-      <c r="Q72" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R72" s="1" t="s">
-        <v>410</v>
-      </c>
+      <c r="Q72" s="1"/>
+      <c r="R72" s="1"/>
       <c r="S72" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T72" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="U72" s="1"/>
-      <c r="V72" s="1"/>
-      <c r="W72" s="1" t="s">
-        <v>411</v>
+      <c r="U72" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V72" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="W72" s="1"/>
+      <c r="X72" s="1"/>
+      <c r="Y72" s="1" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1"/>
+      <c r="L73" s="1"/>
+      <c r="M73" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="F73" s="1" t="s">
+      <c r="N73" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="G73" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
-      <c r="K73" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="L73" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="M73" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N73" s="1"/>
-      <c r="O73" s="1"/>
+      <c r="O73" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P73" s="1"/>
-      <c r="Q73" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R73" s="1" t="s">
-        <v>415</v>
-      </c>
+      <c r="Q73" s="1"/>
+      <c r="R73" s="1"/>
       <c r="S73" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="U73" s="1"/>
-      <c r="V73" s="1"/>
-      <c r="W73" s="1" t="s">
-        <v>411</v>
+        <v>418</v>
+      </c>
+      <c r="U73" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V73" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="W73" s="1"/>
+      <c r="X73" s="1"/>
+      <c r="Y73" s="1" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="J74" s="1"/>
+      <c r="K74" s="1"/>
+      <c r="L74" s="1"/>
+      <c r="M74" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="N74" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="O74" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P74" s="1"/>
+      <c r="Q74" s="1"/>
+      <c r="R74" s="1"/>
+      <c r="S74" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T74" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="U74" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V74" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="1"/>
-      <c r="K74" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="L74" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="M74" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N74" s="1"/>
-      <c r="O74" s="1"/>
-      <c r="P74" s="1"/>
-      <c r="Q74" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R74" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="S74" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="T74" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="U74" s="1"/>
-      <c r="V74" s="1"/>
-      <c r="W74" s="1" t="s">
-        <v>411</v>
+      <c r="W74" s="1"/>
+      <c r="X74" s="1"/>
+      <c r="Y74" s="1" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>409</v>
+        <v>28</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>419</v>
+        <v>29</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
+        <v>412</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J75" s="1"/>
-      <c r="K75" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="L75" s="1" t="s">
-        <v>412</v>
-      </c>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
       <c r="M75" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N75" s="1"/>
-      <c r="O75" s="1"/>
+        <v>414</v>
+      </c>
+      <c r="N75" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="O75" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P75" s="1"/>
-      <c r="Q75" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R75" s="1" t="s">
-        <v>419</v>
-      </c>
+      <c r="Q75" s="1"/>
+      <c r="R75" s="1"/>
       <c r="S75" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="U75" s="1"/>
-      <c r="V75" s="1"/>
-      <c r="W75" s="1" t="s">
-        <v>411</v>
+        <v>422</v>
+      </c>
+      <c r="U75" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V75" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="W75" s="1"/>
+      <c r="X75" s="1"/>
+      <c r="Y75" s="1" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>409</v>
+        <v>28</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>421</v>
+        <v>29</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
+        <v>412</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J76" s="1"/>
-      <c r="K76" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="L76" s="1" t="s">
-        <v>412</v>
-      </c>
+      <c r="K76" s="1"/>
+      <c r="L76" s="1"/>
       <c r="M76" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N76" s="1"/>
-      <c r="O76" s="1"/>
+        <v>414</v>
+      </c>
+      <c r="N76" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="O76" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P76" s="1"/>
-      <c r="Q76" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R76" s="1" t="s">
-        <v>421</v>
-      </c>
+      <c r="Q76" s="1"/>
+      <c r="R76" s="1"/>
       <c r="S76" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="U76" s="1"/>
-      <c r="V76" s="1"/>
-      <c r="W76" s="1" t="s">
-        <v>411</v>
+        <v>424</v>
+      </c>
+      <c r="U76" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V76" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="W76" s="1"/>
+      <c r="X76" s="1"/>
+      <c r="Y76" s="1" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>409</v>
+        <v>28</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>423</v>
+        <v>29</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
+        <v>412</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J77" s="1"/>
-      <c r="K77" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="L77" s="1" t="s">
-        <v>412</v>
-      </c>
+      <c r="K77" s="1"/>
+      <c r="L77" s="1"/>
       <c r="M77" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N77" s="1"/>
-      <c r="O77" s="1"/>
+        <v>414</v>
+      </c>
+      <c r="N77" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="O77" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P77" s="1"/>
-      <c r="Q77" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R77" s="1" t="s">
-        <v>423</v>
-      </c>
+      <c r="Q77" s="1"/>
+      <c r="R77" s="1"/>
       <c r="S77" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="U77" s="1"/>
-      <c r="V77" s="1"/>
-      <c r="W77" s="1" t="s">
-        <v>411</v>
+        <v>426</v>
+      </c>
+      <c r="U77" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V77" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="W77" s="1"/>
+      <c r="X77" s="1"/>
+      <c r="Y77" s="1" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>409</v>
+        <v>28</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>425</v>
+        <v>29</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
+        <v>412</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J78" s="1"/>
-      <c r="K78" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="L78" s="1" t="s">
-        <v>412</v>
-      </c>
+      <c r="K78" s="1"/>
+      <c r="L78" s="1"/>
       <c r="M78" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N78" s="1"/>
-      <c r="O78" s="1"/>
+        <v>414</v>
+      </c>
+      <c r="N78" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="O78" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P78" s="1"/>
-      <c r="Q78" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R78" s="1" t="s">
-        <v>425</v>
-      </c>
+      <c r="Q78" s="1"/>
+      <c r="R78" s="1"/>
       <c r="S78" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="U78" s="1"/>
-      <c r="V78" s="1"/>
-      <c r="W78" s="1" t="s">
-        <v>411</v>
+        <v>428</v>
+      </c>
+      <c r="U78" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V78" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="W78" s="1"/>
+      <c r="X78" s="1"/>
+      <c r="Y78" s="1" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>409</v>
+        <v>28</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>427</v>
+        <v>29</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H79" s="1"/>
-      <c r="I79" s="1"/>
+        <v>412</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
-      <c r="M79" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="M79" s="1"/>
       <c r="N79" s="1"/>
-      <c r="O79" s="1"/>
+      <c r="O79" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P79" s="1"/>
-      <c r="Q79" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R79" s="1" t="s">
-        <v>427</v>
-      </c>
+      <c r="Q79" s="1"/>
+      <c r="R79" s="1"/>
       <c r="S79" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="T79" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="U79" s="1"/>
-      <c r="V79" s="1"/>
+        <v>430</v>
+      </c>
+      <c r="U79" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V79" s="1" t="s">
+        <v>416</v>
+      </c>
       <c r="W79" s="1"/>
+      <c r="X79" s="1"/>
+      <c r="Y79" s="1"/>
     </row>
     <row r="80">
       <c r="A80" s="1"/>
@@ -6145,6 +6630,8 @@
       <c r="U80" s="1"/>
       <c r="V80" s="1"/>
       <c r="W80" s="1"/>
+      <c r="X80" s="1"/>
+      <c r="Y80" s="1"/>
     </row>
     <row r="81">
       <c r="A81" s="1"/>
@@ -6170,6 +6657,8 @@
       <c r="U81" s="1"/>
       <c r="V81" s="1"/>
       <c r="W81" s="1"/>
+      <c r="X81" s="1"/>
+      <c r="Y81" s="1"/>
     </row>
     <row r="82">
       <c r="A82" s="1"/>
@@ -6195,6 +6684,8 @@
       <c r="U82" s="1"/>
       <c r="V82" s="1"/>
       <c r="W82" s="1"/>
+      <c r="X82" s="1"/>
+      <c r="Y82" s="1"/>
     </row>
     <row r="83">
       <c r="A83" s="1"/>
@@ -6220,6 +6711,8 @@
       <c r="U83" s="1"/>
       <c r="V83" s="1"/>
       <c r="W83" s="1"/>
+      <c r="X83" s="1"/>
+      <c r="Y83" s="1"/>
     </row>
     <row r="84">
       <c r="A84" s="1"/>
@@ -6245,6 +6738,8 @@
       <c r="U84" s="1"/>
       <c r="V84" s="1"/>
       <c r="W84" s="1"/>
+      <c r="X84" s="1"/>
+      <c r="Y84" s="1"/>
     </row>
     <row r="85">
       <c r="A85" s="1"/>
@@ -6270,6 +6765,8 @@
       <c r="U85" s="1"/>
       <c r="V85" s="1"/>
       <c r="W85" s="1"/>
+      <c r="X85" s="1"/>
+      <c r="Y85" s="1"/>
     </row>
     <row r="86">
       <c r="A86" s="1"/>
@@ -6295,6 +6792,8 @@
       <c r="U86" s="1"/>
       <c r="V86" s="1"/>
       <c r="W86" s="1"/>
+      <c r="X86" s="1"/>
+      <c r="Y86" s="1"/>
     </row>
     <row r="87">
       <c r="A87" s="1"/>
@@ -6320,6 +6819,8 @@
       <c r="U87" s="1"/>
       <c r="V87" s="1"/>
       <c r="W87" s="1"/>
+      <c r="X87" s="1"/>
+      <c r="Y87" s="1"/>
     </row>
     <row r="88">
       <c r="A88" s="1"/>
@@ -6345,6 +6846,8 @@
       <c r="U88" s="1"/>
       <c r="V88" s="1"/>
       <c r="W88" s="1"/>
+      <c r="X88" s="1"/>
+      <c r="Y88" s="1"/>
     </row>
     <row r="89">
       <c r="A89" s="1"/>
@@ -6370,6 +6873,8 @@
       <c r="U89" s="1"/>
       <c r="V89" s="1"/>
       <c r="W89" s="1"/>
+      <c r="X89" s="1"/>
+      <c r="Y89" s="1"/>
     </row>
     <row r="90">
       <c r="A90" s="1"/>
@@ -6395,6 +6900,8 @@
       <c r="U90" s="1"/>
       <c r="V90" s="1"/>
       <c r="W90" s="1"/>
+      <c r="X90" s="1"/>
+      <c r="Y90" s="1"/>
     </row>
     <row r="91">
       <c r="A91" s="1"/>
@@ -6420,6 +6927,8 @@
       <c r="U91" s="1"/>
       <c r="V91" s="1"/>
       <c r="W91" s="1"/>
+      <c r="X91" s="1"/>
+      <c r="Y91" s="1"/>
     </row>
     <row r="92">
       <c r="A92" s="1"/>
@@ -6445,6 +6954,8 @@
       <c r="U92" s="1"/>
       <c r="V92" s="1"/>
       <c r="W92" s="1"/>
+      <c r="X92" s="1"/>
+      <c r="Y92" s="1"/>
     </row>
     <row r="93">
       <c r="A93" s="1"/>
@@ -6470,6 +6981,8 @@
       <c r="U93" s="1"/>
       <c r="V93" s="1"/>
       <c r="W93" s="1"/>
+      <c r="X93" s="1"/>
+      <c r="Y93" s="1"/>
     </row>
     <row r="94">
       <c r="A94" s="1"/>
@@ -6495,6 +7008,8 @@
       <c r="U94" s="1"/>
       <c r="V94" s="1"/>
       <c r="W94" s="1"/>
+      <c r="X94" s="1"/>
+      <c r="Y94" s="1"/>
     </row>
     <row r="95">
       <c r="A95" s="1"/>
@@ -6520,6 +7035,8 @@
       <c r="U95" s="1"/>
       <c r="V95" s="1"/>
       <c r="W95" s="1"/>
+      <c r="X95" s="1"/>
+      <c r="Y95" s="1"/>
     </row>
     <row r="96">
       <c r="A96" s="1"/>
@@ -6545,6 +7062,8 @@
       <c r="U96" s="1"/>
       <c r="V96" s="1"/>
       <c r="W96" s="1"/>
+      <c r="X96" s="1"/>
+      <c r="Y96" s="1"/>
     </row>
     <row r="97">
       <c r="A97" s="1"/>
@@ -6570,6 +7089,8 @@
       <c r="U97" s="1"/>
       <c r="V97" s="1"/>
       <c r="W97" s="1"/>
+      <c r="X97" s="1"/>
+      <c r="Y97" s="1"/>
     </row>
     <row r="98">
       <c r="A98" s="1"/>
@@ -6595,6 +7116,8 @@
       <c r="U98" s="1"/>
       <c r="V98" s="1"/>
       <c r="W98" s="1"/>
+      <c r="X98" s="1"/>
+      <c r="Y98" s="1"/>
     </row>
     <row r="99">
       <c r="A99" s="1"/>
@@ -6620,6 +7143,8 @@
       <c r="U99" s="1"/>
       <c r="V99" s="1"/>
       <c r="W99" s="1"/>
+      <c r="X99" s="1"/>
+      <c r="Y99" s="1"/>
     </row>
     <row r="100">
       <c r="A100" s="1"/>
@@ -6645,6 +7170,8 @@
       <c r="U100" s="1"/>
       <c r="V100" s="1"/>
       <c r="W100" s="1"/>
+      <c r="X100" s="1"/>
+      <c r="Y100" s="1"/>
     </row>
     <row r="101">
       <c r="A101" s="1"/>
@@ -6670,6 +7197,8 @@
       <c r="U101" s="1"/>
       <c r="V101" s="1"/>
       <c r="W101" s="1"/>
+      <c r="X101" s="1"/>
+      <c r="Y101" s="1"/>
     </row>
     <row r="102">
       <c r="A102" s="1"/>
@@ -6695,6 +7224,8 @@
       <c r="U102" s="1"/>
       <c r="V102" s="1"/>
       <c r="W102" s="1"/>
+      <c r="X102" s="1"/>
+      <c r="Y102" s="1"/>
     </row>
     <row r="103">
       <c r="A103" s="1"/>
@@ -6720,6 +7251,8 @@
       <c r="U103" s="1"/>
       <c r="V103" s="1"/>
       <c r="W103" s="1"/>
+      <c r="X103" s="1"/>
+      <c r="Y103" s="1"/>
     </row>
     <row r="104">
       <c r="A104" s="1"/>
@@ -6745,6 +7278,8 @@
       <c r="U104" s="1"/>
       <c r="V104" s="1"/>
       <c r="W104" s="1"/>
+      <c r="X104" s="1"/>
+      <c r="Y104" s="1"/>
     </row>
     <row r="105">
       <c r="A105" s="1"/>
@@ -6770,6 +7305,8 @@
       <c r="U105" s="1"/>
       <c r="V105" s="1"/>
       <c r="W105" s="1"/>
+      <c r="X105" s="1"/>
+      <c r="Y105" s="1"/>
     </row>
     <row r="106">
       <c r="A106" s="1"/>
@@ -6795,6 +7332,8 @@
       <c r="U106" s="1"/>
       <c r="V106" s="1"/>
       <c r="W106" s="1"/>
+      <c r="X106" s="1"/>
+      <c r="Y106" s="1"/>
     </row>
     <row r="107">
       <c r="A107" s="1"/>
@@ -6820,6 +7359,8 @@
       <c r="U107" s="1"/>
       <c r="V107" s="1"/>
       <c r="W107" s="1"/>
+      <c r="X107" s="1"/>
+      <c r="Y107" s="1"/>
     </row>
     <row r="108">
       <c r="A108" s="1"/>
@@ -6845,6 +7386,8 @@
       <c r="U108" s="1"/>
       <c r="V108" s="1"/>
       <c r="W108" s="1"/>
+      <c r="X108" s="1"/>
+      <c r="Y108" s="1"/>
     </row>
     <row r="109">
       <c r="A109" s="1"/>
@@ -6870,6 +7413,8 @@
       <c r="U109" s="1"/>
       <c r="V109" s="1"/>
       <c r="W109" s="1"/>
+      <c r="X109" s="1"/>
+      <c r="Y109" s="1"/>
     </row>
     <row r="110">
       <c r="A110" s="1"/>
@@ -6895,6 +7440,8 @@
       <c r="U110" s="1"/>
       <c r="V110" s="1"/>
       <c r="W110" s="1"/>
+      <c r="X110" s="1"/>
+      <c r="Y110" s="1"/>
     </row>
     <row r="111">
       <c r="A111" s="1"/>
@@ -6920,6 +7467,8 @@
       <c r="U111" s="1"/>
       <c r="V111" s="1"/>
       <c r="W111" s="1"/>
+      <c r="X111" s="1"/>
+      <c r="Y111" s="1"/>
     </row>
     <row r="112">
       <c r="A112" s="1"/>
@@ -6945,6 +7494,8 @@
       <c r="U112" s="1"/>
       <c r="V112" s="1"/>
       <c r="W112" s="1"/>
+      <c r="X112" s="1"/>
+      <c r="Y112" s="1"/>
     </row>
     <row r="113">
       <c r="A113" s="1"/>
@@ -6970,6 +7521,8 @@
       <c r="U113" s="1"/>
       <c r="V113" s="1"/>
       <c r="W113" s="1"/>
+      <c r="X113" s="1"/>
+      <c r="Y113" s="1"/>
     </row>
     <row r="114">
       <c r="A114" s="1"/>
@@ -6995,6 +7548,8 @@
       <c r="U114" s="1"/>
       <c r="V114" s="1"/>
       <c r="W114" s="1"/>
+      <c r="X114" s="1"/>
+      <c r="Y114" s="1"/>
     </row>
     <row r="115">
       <c r="A115" s="1"/>
@@ -7020,6 +7575,8 @@
       <c r="U115" s="1"/>
       <c r="V115" s="1"/>
       <c r="W115" s="1"/>
+      <c r="X115" s="1"/>
+      <c r="Y115" s="1"/>
     </row>
     <row r="116">
       <c r="A116" s="1"/>
@@ -7045,6 +7602,8 @@
       <c r="U116" s="1"/>
       <c r="V116" s="1"/>
       <c r="W116" s="1"/>
+      <c r="X116" s="1"/>
+      <c r="Y116" s="1"/>
     </row>
     <row r="117">
       <c r="A117" s="1"/>
@@ -7070,6 +7629,8 @@
       <c r="U117" s="1"/>
       <c r="V117" s="1"/>
       <c r="W117" s="1"/>
+      <c r="X117" s="1"/>
+      <c r="Y117" s="1"/>
     </row>
     <row r="118">
       <c r="A118" s="1"/>
@@ -7095,6 +7656,8 @@
       <c r="U118" s="1"/>
       <c r="V118" s="1"/>
       <c r="W118" s="1"/>
+      <c r="X118" s="1"/>
+      <c r="Y118" s="1"/>
     </row>
     <row r="119">
       <c r="A119" s="1"/>
@@ -7120,6 +7683,8 @@
       <c r="U119" s="1"/>
       <c r="V119" s="1"/>
       <c r="W119" s="1"/>
+      <c r="X119" s="1"/>
+      <c r="Y119" s="1"/>
     </row>
     <row r="120">
       <c r="A120" s="1"/>
@@ -7145,6 +7710,8 @@
       <c r="U120" s="1"/>
       <c r="V120" s="1"/>
       <c r="W120" s="1"/>
+      <c r="X120" s="1"/>
+      <c r="Y120" s="1"/>
     </row>
     <row r="121">
       <c r="A121" s="1"/>
@@ -7170,6 +7737,8 @@
       <c r="U121" s="1"/>
       <c r="V121" s="1"/>
       <c r="W121" s="1"/>
+      <c r="X121" s="1"/>
+      <c r="Y121" s="1"/>
     </row>
     <row r="122">
       <c r="A122" s="1"/>
@@ -7195,6 +7764,8 @@
       <c r="U122" s="1"/>
       <c r="V122" s="1"/>
       <c r="W122" s="1"/>
+      <c r="X122" s="1"/>
+      <c r="Y122" s="1"/>
     </row>
     <row r="123">
       <c r="A123" s="1"/>
@@ -7220,6 +7791,8 @@
       <c r="U123" s="1"/>
       <c r="V123" s="1"/>
       <c r="W123" s="1"/>
+      <c r="X123" s="1"/>
+      <c r="Y123" s="1"/>
     </row>
     <row r="124">
       <c r="A124" s="1"/>
@@ -7245,6 +7818,8 @@
       <c r="U124" s="1"/>
       <c r="V124" s="1"/>
       <c r="W124" s="1"/>
+      <c r="X124" s="1"/>
+      <c r="Y124" s="1"/>
     </row>
     <row r="125">
       <c r="A125" s="1"/>
@@ -7270,6 +7845,8 @@
       <c r="U125" s="1"/>
       <c r="V125" s="1"/>
       <c r="W125" s="1"/>
+      <c r="X125" s="1"/>
+      <c r="Y125" s="1"/>
     </row>
     <row r="126">
       <c r="A126" s="1"/>
@@ -7295,6 +7872,8 @@
       <c r="U126" s="1"/>
       <c r="V126" s="1"/>
       <c r="W126" s="1"/>
+      <c r="X126" s="1"/>
+      <c r="Y126" s="1"/>
     </row>
     <row r="127">
       <c r="A127" s="1"/>
@@ -7320,6 +7899,8 @@
       <c r="U127" s="1"/>
       <c r="V127" s="1"/>
       <c r="W127" s="1"/>
+      <c r="X127" s="1"/>
+      <c r="Y127" s="1"/>
     </row>
     <row r="128">
       <c r="A128" s="1"/>
@@ -7345,6 +7926,8 @@
       <c r="U128" s="1"/>
       <c r="V128" s="1"/>
       <c r="W128" s="1"/>
+      <c r="X128" s="1"/>
+      <c r="Y128" s="1"/>
     </row>
     <row r="129">
       <c r="A129" s="1"/>
@@ -7370,6 +7953,8 @@
       <c r="U129" s="1"/>
       <c r="V129" s="1"/>
       <c r="W129" s="1"/>
+      <c r="X129" s="1"/>
+      <c r="Y129" s="1"/>
     </row>
     <row r="130">
       <c r="A130" s="1"/>
@@ -7395,6 +7980,8 @@
       <c r="U130" s="1"/>
       <c r="V130" s="1"/>
       <c r="W130" s="1"/>
+      <c r="X130" s="1"/>
+      <c r="Y130" s="1"/>
     </row>
     <row r="131">
       <c r="A131" s="1"/>
@@ -7420,6 +8007,8 @@
       <c r="U131" s="1"/>
       <c r="V131" s="1"/>
       <c r="W131" s="1"/>
+      <c r="X131" s="1"/>
+      <c r="Y131" s="1"/>
     </row>
     <row r="132">
       <c r="A132" s="1"/>
@@ -7445,6 +8034,8 @@
       <c r="U132" s="1"/>
       <c r="V132" s="1"/>
       <c r="W132" s="1"/>
+      <c r="X132" s="1"/>
+      <c r="Y132" s="1"/>
     </row>
     <row r="133">
       <c r="A133" s="1"/>
@@ -7470,6 +8061,8 @@
       <c r="U133" s="1"/>
       <c r="V133" s="1"/>
       <c r="W133" s="1"/>
+      <c r="X133" s="1"/>
+      <c r="Y133" s="1"/>
     </row>
     <row r="134">
       <c r="A134" s="1"/>
@@ -7495,6 +8088,8 @@
       <c r="U134" s="1"/>
       <c r="V134" s="1"/>
       <c r="W134" s="1"/>
+      <c r="X134" s="1"/>
+      <c r="Y134" s="1"/>
     </row>
     <row r="135">
       <c r="A135" s="1"/>
@@ -7520,6 +8115,8 @@
       <c r="U135" s="1"/>
       <c r="V135" s="1"/>
       <c r="W135" s="1"/>
+      <c r="X135" s="1"/>
+      <c r="Y135" s="1"/>
     </row>
     <row r="136">
       <c r="A136" s="1"/>
@@ -7545,6 +8142,8 @@
       <c r="U136" s="1"/>
       <c r="V136" s="1"/>
       <c r="W136" s="1"/>
+      <c r="X136" s="1"/>
+      <c r="Y136" s="1"/>
     </row>
     <row r="137">
       <c r="A137" s="1"/>
@@ -7570,6 +8169,8 @@
       <c r="U137" s="1"/>
       <c r="V137" s="1"/>
       <c r="W137" s="1"/>
+      <c r="X137" s="1"/>
+      <c r="Y137" s="1"/>
     </row>
     <row r="138">
       <c r="A138" s="1"/>
@@ -7595,6 +8196,8 @@
       <c r="U138" s="1"/>
       <c r="V138" s="1"/>
       <c r="W138" s="1"/>
+      <c r="X138" s="1"/>
+      <c r="Y138" s="1"/>
     </row>
     <row r="139">
       <c r="A139" s="1"/>
@@ -7620,6 +8223,8 @@
       <c r="U139" s="1"/>
       <c r="V139" s="1"/>
       <c r="W139" s="1"/>
+      <c r="X139" s="1"/>
+      <c r="Y139" s="1"/>
     </row>
     <row r="140">
       <c r="A140" s="1"/>
@@ -7645,6 +8250,8 @@
       <c r="U140" s="1"/>
       <c r="V140" s="1"/>
       <c r="W140" s="1"/>
+      <c r="X140" s="1"/>
+      <c r="Y140" s="1"/>
     </row>
     <row r="141">
       <c r="A141" s="1"/>
@@ -7670,6 +8277,8 @@
       <c r="U141" s="1"/>
       <c r="V141" s="1"/>
       <c r="W141" s="1"/>
+      <c r="X141" s="1"/>
+      <c r="Y141" s="1"/>
     </row>
     <row r="142">
       <c r="A142" s="1"/>
@@ -7695,6 +8304,8 @@
       <c r="U142" s="1"/>
       <c r="V142" s="1"/>
       <c r="W142" s="1"/>
+      <c r="X142" s="1"/>
+      <c r="Y142" s="1"/>
     </row>
     <row r="143">
       <c r="A143" s="1"/>
@@ -7720,6 +8331,8 @@
       <c r="U143" s="1"/>
       <c r="V143" s="1"/>
       <c r="W143" s="1"/>
+      <c r="X143" s="1"/>
+      <c r="Y143" s="1"/>
     </row>
     <row r="144">
       <c r="A144" s="1"/>
@@ -7745,6 +8358,8 @@
       <c r="U144" s="1"/>
       <c r="V144" s="1"/>
       <c r="W144" s="1"/>
+      <c r="X144" s="1"/>
+      <c r="Y144" s="1"/>
     </row>
     <row r="145">
       <c r="A145" s="1"/>
@@ -7770,6 +8385,8 @@
       <c r="U145" s="1"/>
       <c r="V145" s="1"/>
       <c r="W145" s="1"/>
+      <c r="X145" s="1"/>
+      <c r="Y145" s="1"/>
     </row>
     <row r="146">
       <c r="A146" s="1"/>
@@ -7795,6 +8412,8 @@
       <c r="U146" s="1"/>
       <c r="V146" s="1"/>
       <c r="W146" s="1"/>
+      <c r="X146" s="1"/>
+      <c r="Y146" s="1"/>
     </row>
     <row r="147">
       <c r="A147" s="1"/>
@@ -7820,6 +8439,8 @@
       <c r="U147" s="1"/>
       <c r="V147" s="1"/>
       <c r="W147" s="1"/>
+      <c r="X147" s="1"/>
+      <c r="Y147" s="1"/>
     </row>
     <row r="148">
       <c r="A148" s="1"/>
@@ -7845,6 +8466,8 @@
       <c r="U148" s="1"/>
       <c r="V148" s="1"/>
       <c r="W148" s="1"/>
+      <c r="X148" s="1"/>
+      <c r="Y148" s="1"/>
     </row>
     <row r="149">
       <c r="A149" s="1"/>
@@ -7870,6 +8493,8 @@
       <c r="U149" s="1"/>
       <c r="V149" s="1"/>
       <c r="W149" s="1"/>
+      <c r="X149" s="1"/>
+      <c r="Y149" s="1"/>
     </row>
     <row r="150">
       <c r="A150" s="1"/>
@@ -7895,6 +8520,8 @@
       <c r="U150" s="1"/>
       <c r="V150" s="1"/>
       <c r="W150" s="1"/>
+      <c r="X150" s="1"/>
+      <c r="Y150" s="1"/>
     </row>
     <row r="151">
       <c r="A151" s="1"/>
@@ -7920,6 +8547,8 @@
       <c r="U151" s="1"/>
       <c r="V151" s="1"/>
       <c r="W151" s="1"/>
+      <c r="X151" s="1"/>
+      <c r="Y151" s="1"/>
     </row>
     <row r="152">
       <c r="A152" s="1"/>
@@ -7945,6 +8574,8 @@
       <c r="U152" s="1"/>
       <c r="V152" s="1"/>
       <c r="W152" s="1"/>
+      <c r="X152" s="1"/>
+      <c r="Y152" s="1"/>
     </row>
     <row r="153">
       <c r="A153" s="1"/>
@@ -7970,6 +8601,8 @@
       <c r="U153" s="1"/>
       <c r="V153" s="1"/>
       <c r="W153" s="1"/>
+      <c r="X153" s="1"/>
+      <c r="Y153" s="1"/>
     </row>
     <row r="154">
       <c r="A154" s="1"/>
@@ -7995,6 +8628,8 @@
       <c r="U154" s="1"/>
       <c r="V154" s="1"/>
       <c r="W154" s="1"/>
+      <c r="X154" s="1"/>
+      <c r="Y154" s="1"/>
     </row>
     <row r="155">
       <c r="A155" s="1"/>
@@ -8020,6 +8655,8 @@
       <c r="U155" s="1"/>
       <c r="V155" s="1"/>
       <c r="W155" s="1"/>
+      <c r="X155" s="1"/>
+      <c r="Y155" s="1"/>
     </row>
     <row r="156">
       <c r="A156" s="1"/>
@@ -8045,6 +8682,8 @@
       <c r="U156" s="1"/>
       <c r="V156" s="1"/>
       <c r="W156" s="1"/>
+      <c r="X156" s="1"/>
+      <c r="Y156" s="1"/>
     </row>
     <row r="157">
       <c r="A157" s="1"/>
@@ -8070,6 +8709,8 @@
       <c r="U157" s="1"/>
       <c r="V157" s="1"/>
       <c r="W157" s="1"/>
+      <c r="X157" s="1"/>
+      <c r="Y157" s="1"/>
     </row>
     <row r="158">
       <c r="A158" s="1"/>
@@ -8095,6 +8736,8 @@
       <c r="U158" s="1"/>
       <c r="V158" s="1"/>
       <c r="W158" s="1"/>
+      <c r="X158" s="1"/>
+      <c r="Y158" s="1"/>
     </row>
     <row r="159">
       <c r="A159" s="1"/>
@@ -8120,6 +8763,8 @@
       <c r="U159" s="1"/>
       <c r="V159" s="1"/>
       <c r="W159" s="1"/>
+      <c r="X159" s="1"/>
+      <c r="Y159" s="1"/>
     </row>
     <row r="160">
       <c r="A160" s="1"/>
@@ -8145,6 +8790,8 @@
       <c r="U160" s="1"/>
       <c r="V160" s="1"/>
       <c r="W160" s="1"/>
+      <c r="X160" s="1"/>
+      <c r="Y160" s="1"/>
     </row>
     <row r="161">
       <c r="A161" s="1"/>
@@ -8170,6 +8817,8 @@
       <c r="U161" s="1"/>
       <c r="V161" s="1"/>
       <c r="W161" s="1"/>
+      <c r="X161" s="1"/>
+      <c r="Y161" s="1"/>
     </row>
     <row r="162">
       <c r="A162" s="1"/>
@@ -8195,6 +8844,8 @@
       <c r="U162" s="1"/>
       <c r="V162" s="1"/>
       <c r="W162" s="1"/>
+      <c r="X162" s="1"/>
+      <c r="Y162" s="1"/>
     </row>
     <row r="163">
       <c r="A163" s="1"/>
@@ -8220,6 +8871,8 @@
       <c r="U163" s="1"/>
       <c r="V163" s="1"/>
       <c r="W163" s="1"/>
+      <c r="X163" s="1"/>
+      <c r="Y163" s="1"/>
     </row>
     <row r="164">
       <c r="A164" s="1"/>
@@ -8245,6 +8898,8 @@
       <c r="U164" s="1"/>
       <c r="V164" s="1"/>
       <c r="W164" s="1"/>
+      <c r="X164" s="1"/>
+      <c r="Y164" s="1"/>
     </row>
     <row r="165">
       <c r="A165" s="1"/>
@@ -8270,6 +8925,8 @@
       <c r="U165" s="1"/>
       <c r="V165" s="1"/>
       <c r="W165" s="1"/>
+      <c r="X165" s="1"/>
+      <c r="Y165" s="1"/>
     </row>
     <row r="166">
       <c r="A166" s="1"/>
@@ -8295,6 +8952,8 @@
       <c r="U166" s="1"/>
       <c r="V166" s="1"/>
       <c r="W166" s="1"/>
+      <c r="X166" s="1"/>
+      <c r="Y166" s="1"/>
     </row>
     <row r="167">
       <c r="A167" s="1"/>
@@ -8320,6 +8979,8 @@
       <c r="U167" s="1"/>
       <c r="V167" s="1"/>
       <c r="W167" s="1"/>
+      <c r="X167" s="1"/>
+      <c r="Y167" s="1"/>
     </row>
     <row r="168">
       <c r="A168" s="1"/>
@@ -8345,6 +9006,8 @@
       <c r="U168" s="1"/>
       <c r="V168" s="1"/>
       <c r="W168" s="1"/>
+      <c r="X168" s="1"/>
+      <c r="Y168" s="1"/>
     </row>
     <row r="169">
       <c r="A169" s="1"/>
@@ -8370,6 +9033,8 @@
       <c r="U169" s="1"/>
       <c r="V169" s="1"/>
       <c r="W169" s="1"/>
+      <c r="X169" s="1"/>
+      <c r="Y169" s="1"/>
     </row>
     <row r="170">
       <c r="A170" s="1"/>
@@ -8395,6 +9060,8 @@
       <c r="U170" s="1"/>
       <c r="V170" s="1"/>
       <c r="W170" s="1"/>
+      <c r="X170" s="1"/>
+      <c r="Y170" s="1"/>
     </row>
     <row r="171">
       <c r="A171" s="1"/>
@@ -8420,6 +9087,8 @@
       <c r="U171" s="1"/>
       <c r="V171" s="1"/>
       <c r="W171" s="1"/>
+      <c r="X171" s="1"/>
+      <c r="Y171" s="1"/>
     </row>
     <row r="172">
       <c r="A172" s="1"/>
@@ -8445,6 +9114,8 @@
       <c r="U172" s="1"/>
       <c r="V172" s="1"/>
       <c r="W172" s="1"/>
+      <c r="X172" s="1"/>
+      <c r="Y172" s="1"/>
     </row>
     <row r="173">
       <c r="A173" s="1"/>
@@ -8470,6 +9141,8 @@
       <c r="U173" s="1"/>
       <c r="V173" s="1"/>
       <c r="W173" s="1"/>
+      <c r="X173" s="1"/>
+      <c r="Y173" s="1"/>
     </row>
     <row r="174">
       <c r="A174" s="1"/>
@@ -8495,6 +9168,8 @@
       <c r="U174" s="1"/>
       <c r="V174" s="1"/>
       <c r="W174" s="1"/>
+      <c r="X174" s="1"/>
+      <c r="Y174" s="1"/>
     </row>
     <row r="175">
       <c r="A175" s="1"/>
@@ -8520,6 +9195,8 @@
       <c r="U175" s="1"/>
       <c r="V175" s="1"/>
       <c r="W175" s="1"/>
+      <c r="X175" s="1"/>
+      <c r="Y175" s="1"/>
     </row>
     <row r="176">
       <c r="A176" s="1"/>
@@ -8545,6 +9222,8 @@
       <c r="U176" s="1"/>
       <c r="V176" s="1"/>
       <c r="W176" s="1"/>
+      <c r="X176" s="1"/>
+      <c r="Y176" s="1"/>
     </row>
     <row r="177">
       <c r="A177" s="1"/>
@@ -8570,6 +9249,8 @@
       <c r="U177" s="1"/>
       <c r="V177" s="1"/>
       <c r="W177" s="1"/>
+      <c r="X177" s="1"/>
+      <c r="Y177" s="1"/>
     </row>
     <row r="178">
       <c r="A178" s="1"/>
@@ -8595,6 +9276,8 @@
       <c r="U178" s="1"/>
       <c r="V178" s="1"/>
       <c r="W178" s="1"/>
+      <c r="X178" s="1"/>
+      <c r="Y178" s="1"/>
     </row>
     <row r="179">
       <c r="A179" s="1"/>
@@ -8620,6 +9303,8 @@
       <c r="U179" s="1"/>
       <c r="V179" s="1"/>
       <c r="W179" s="1"/>
+      <c r="X179" s="1"/>
+      <c r="Y179" s="1"/>
     </row>
     <row r="180">
       <c r="A180" s="1"/>
@@ -8645,6 +9330,8 @@
       <c r="U180" s="1"/>
       <c r="V180" s="1"/>
       <c r="W180" s="1"/>
+      <c r="X180" s="1"/>
+      <c r="Y180" s="1"/>
     </row>
     <row r="181">
       <c r="A181" s="1"/>
@@ -8670,6 +9357,8 @@
       <c r="U181" s="1"/>
       <c r="V181" s="1"/>
       <c r="W181" s="1"/>
+      <c r="X181" s="1"/>
+      <c r="Y181" s="1"/>
     </row>
     <row r="182">
       <c r="A182" s="1"/>
@@ -8695,6 +9384,8 @@
       <c r="U182" s="1"/>
       <c r="V182" s="1"/>
       <c r="W182" s="1"/>
+      <c r="X182" s="1"/>
+      <c r="Y182" s="1"/>
     </row>
     <row r="183">
       <c r="A183" s="1"/>
@@ -8720,6 +9411,8 @@
       <c r="U183" s="1"/>
       <c r="V183" s="1"/>
       <c r="W183" s="1"/>
+      <c r="X183" s="1"/>
+      <c r="Y183" s="1"/>
     </row>
     <row r="184">
       <c r="A184" s="1"/>
@@ -8745,6 +9438,8 @@
       <c r="U184" s="1"/>
       <c r="V184" s="1"/>
       <c r="W184" s="1"/>
+      <c r="X184" s="1"/>
+      <c r="Y184" s="1"/>
     </row>
     <row r="185">
       <c r="A185" s="1"/>
@@ -8770,6 +9465,8 @@
       <c r="U185" s="1"/>
       <c r="V185" s="1"/>
       <c r="W185" s="1"/>
+      <c r="X185" s="1"/>
+      <c r="Y185" s="1"/>
     </row>
     <row r="186">
       <c r="A186" s="1"/>
@@ -8795,6 +9492,8 @@
       <c r="U186" s="1"/>
       <c r="V186" s="1"/>
       <c r="W186" s="1"/>
+      <c r="X186" s="1"/>
+      <c r="Y186" s="1"/>
     </row>
     <row r="187">
       <c r="A187" s="1"/>
@@ -8820,6 +9519,8 @@
       <c r="U187" s="1"/>
       <c r="V187" s="1"/>
       <c r="W187" s="1"/>
+      <c r="X187" s="1"/>
+      <c r="Y187" s="1"/>
     </row>
     <row r="188">
       <c r="A188" s="1"/>
@@ -8845,6 +9546,8 @@
       <c r="U188" s="1"/>
       <c r="V188" s="1"/>
       <c r="W188" s="1"/>
+      <c r="X188" s="1"/>
+      <c r="Y188" s="1"/>
     </row>
     <row r="189">
       <c r="A189" s="1"/>
@@ -8870,6 +9573,8 @@
       <c r="U189" s="1"/>
       <c r="V189" s="1"/>
       <c r="W189" s="1"/>
+      <c r="X189" s="1"/>
+      <c r="Y189" s="1"/>
     </row>
     <row r="190">
       <c r="A190" s="1"/>
@@ -8895,6 +9600,8 @@
       <c r="U190" s="1"/>
       <c r="V190" s="1"/>
       <c r="W190" s="1"/>
+      <c r="X190" s="1"/>
+      <c r="Y190" s="1"/>
     </row>
     <row r="191">
       <c r="A191" s="1"/>
@@ -8920,6 +9627,8 @@
       <c r="U191" s="1"/>
       <c r="V191" s="1"/>
       <c r="W191" s="1"/>
+      <c r="X191" s="1"/>
+      <c r="Y191" s="1"/>
     </row>
     <row r="192">
       <c r="A192" s="1"/>
@@ -8945,6 +9654,8 @@
       <c r="U192" s="1"/>
       <c r="V192" s="1"/>
       <c r="W192" s="1"/>
+      <c r="X192" s="1"/>
+      <c r="Y192" s="1"/>
     </row>
     <row r="193">
       <c r="A193" s="1"/>
@@ -8970,6 +9681,8 @@
       <c r="U193" s="1"/>
       <c r="V193" s="1"/>
       <c r="W193" s="1"/>
+      <c r="X193" s="1"/>
+      <c r="Y193" s="1"/>
     </row>
     <row r="194">
       <c r="A194" s="1"/>
@@ -8995,6 +9708,8 @@
       <c r="U194" s="1"/>
       <c r="V194" s="1"/>
       <c r="W194" s="1"/>
+      <c r="X194" s="1"/>
+      <c r="Y194" s="1"/>
     </row>
     <row r="195">
       <c r="A195" s="1"/>
@@ -9020,6 +9735,8 @@
       <c r="U195" s="1"/>
       <c r="V195" s="1"/>
       <c r="W195" s="1"/>
+      <c r="X195" s="1"/>
+      <c r="Y195" s="1"/>
     </row>
     <row r="196">
       <c r="A196" s="1"/>
@@ -9045,6 +9762,8 @@
       <c r="U196" s="1"/>
       <c r="V196" s="1"/>
       <c r="W196" s="1"/>
+      <c r="X196" s="1"/>
+      <c r="Y196" s="1"/>
     </row>
     <row r="197">
       <c r="A197" s="1"/>
@@ -9070,6 +9789,8 @@
       <c r="U197" s="1"/>
       <c r="V197" s="1"/>
       <c r="W197" s="1"/>
+      <c r="X197" s="1"/>
+      <c r="Y197" s="1"/>
     </row>
     <row r="198">
       <c r="A198" s="1"/>
@@ -9095,6 +9816,8 @@
       <c r="U198" s="1"/>
       <c r="V198" s="1"/>
       <c r="W198" s="1"/>
+      <c r="X198" s="1"/>
+      <c r="Y198" s="1"/>
     </row>
     <row r="199">
       <c r="A199" s="1"/>
@@ -9120,6 +9843,8 @@
       <c r="U199" s="1"/>
       <c r="V199" s="1"/>
       <c r="W199" s="1"/>
+      <c r="X199" s="1"/>
+      <c r="Y199" s="1"/>
     </row>
     <row r="200">
       <c r="A200" s="1"/>
@@ -9145,6 +9870,8 @@
       <c r="U200" s="1"/>
       <c r="V200" s="1"/>
       <c r="W200" s="1"/>
+      <c r="X200" s="1"/>
+      <c r="Y200" s="1"/>
     </row>
     <row r="201">
       <c r="A201" s="1"/>
@@ -9170,6 +9897,8 @@
       <c r="U201" s="1"/>
       <c r="V201" s="1"/>
       <c r="W201" s="1"/>
+      <c r="X201" s="1"/>
+      <c r="Y201" s="1"/>
     </row>
     <row r="202">
       <c r="A202" s="1"/>
@@ -9195,6 +9924,8 @@
       <c r="U202" s="1"/>
       <c r="V202" s="1"/>
       <c r="W202" s="1"/>
+      <c r="X202" s="1"/>
+      <c r="Y202" s="1"/>
     </row>
     <row r="203">
       <c r="A203" s="1"/>
@@ -9220,6 +9951,8 @@
       <c r="U203" s="1"/>
       <c r="V203" s="1"/>
       <c r="W203" s="1"/>
+      <c r="X203" s="1"/>
+      <c r="Y203" s="1"/>
     </row>
     <row r="204">
       <c r="A204" s="1"/>
@@ -9245,6 +9978,8 @@
       <c r="U204" s="1"/>
       <c r="V204" s="1"/>
       <c r="W204" s="1"/>
+      <c r="X204" s="1"/>
+      <c r="Y204" s="1"/>
     </row>
     <row r="205">
       <c r="A205" s="1"/>
@@ -9270,6 +10005,8 @@
       <c r="U205" s="1"/>
       <c r="V205" s="1"/>
       <c r="W205" s="1"/>
+      <c r="X205" s="1"/>
+      <c r="Y205" s="1"/>
     </row>
     <row r="206">
       <c r="A206" s="1"/>
@@ -9295,6 +10032,8 @@
       <c r="U206" s="1"/>
       <c r="V206" s="1"/>
       <c r="W206" s="1"/>
+      <c r="X206" s="1"/>
+      <c r="Y206" s="1"/>
     </row>
     <row r="207">
       <c r="A207" s="1"/>
@@ -9320,6 +10059,8 @@
       <c r="U207" s="1"/>
       <c r="V207" s="1"/>
       <c r="W207" s="1"/>
+      <c r="X207" s="1"/>
+      <c r="Y207" s="1"/>
     </row>
     <row r="208">
       <c r="A208" s="1"/>
@@ -9345,6 +10086,8 @@
       <c r="U208" s="1"/>
       <c r="V208" s="1"/>
       <c r="W208" s="1"/>
+      <c r="X208" s="1"/>
+      <c r="Y208" s="1"/>
     </row>
     <row r="209">
       <c r="A209" s="1"/>
@@ -9370,6 +10113,8 @@
       <c r="U209" s="1"/>
       <c r="V209" s="1"/>
       <c r="W209" s="1"/>
+      <c r="X209" s="1"/>
+      <c r="Y209" s="1"/>
     </row>
     <row r="210">
       <c r="A210" s="1"/>
@@ -9395,6 +10140,8 @@
       <c r="U210" s="1"/>
       <c r="V210" s="1"/>
       <c r="W210" s="1"/>
+      <c r="X210" s="1"/>
+      <c r="Y210" s="1"/>
     </row>
     <row r="211">
       <c r="A211" s="1"/>
@@ -9420,6 +10167,8 @@
       <c r="U211" s="1"/>
       <c r="V211" s="1"/>
       <c r="W211" s="1"/>
+      <c r="X211" s="1"/>
+      <c r="Y211" s="1"/>
     </row>
     <row r="212">
       <c r="A212" s="1"/>
@@ -9445,6 +10194,8 @@
       <c r="U212" s="1"/>
       <c r="V212" s="1"/>
       <c r="W212" s="1"/>
+      <c r="X212" s="1"/>
+      <c r="Y212" s="1"/>
     </row>
     <row r="213">
       <c r="A213" s="1"/>
@@ -9470,6 +10221,8 @@
       <c r="U213" s="1"/>
       <c r="V213" s="1"/>
       <c r="W213" s="1"/>
+      <c r="X213" s="1"/>
+      <c r="Y213" s="1"/>
     </row>
     <row r="214">
       <c r="A214" s="1"/>
@@ -9495,6 +10248,8 @@
       <c r="U214" s="1"/>
       <c r="V214" s="1"/>
       <c r="W214" s="1"/>
+      <c r="X214" s="1"/>
+      <c r="Y214" s="1"/>
     </row>
     <row r="215">
       <c r="A215" s="1"/>
@@ -9520,6 +10275,8 @@
       <c r="U215" s="1"/>
       <c r="V215" s="1"/>
       <c r="W215" s="1"/>
+      <c r="X215" s="1"/>
+      <c r="Y215" s="1"/>
     </row>
     <row r="216">
       <c r="A216" s="1"/>
@@ -9545,6 +10302,8 @@
       <c r="U216" s="1"/>
       <c r="V216" s="1"/>
       <c r="W216" s="1"/>
+      <c r="X216" s="1"/>
+      <c r="Y216" s="1"/>
     </row>
     <row r="217">
       <c r="A217" s="1"/>
@@ -9570,6 +10329,8 @@
       <c r="U217" s="1"/>
       <c r="V217" s="1"/>
       <c r="W217" s="1"/>
+      <c r="X217" s="1"/>
+      <c r="Y217" s="1"/>
     </row>
     <row r="218">
       <c r="A218" s="1"/>
@@ -9595,6 +10356,8 @@
       <c r="U218" s="1"/>
       <c r="V218" s="1"/>
       <c r="W218" s="1"/>
+      <c r="X218" s="1"/>
+      <c r="Y218" s="1"/>
     </row>
     <row r="219">
       <c r="A219" s="1"/>
@@ -9620,6 +10383,8 @@
       <c r="U219" s="1"/>
       <c r="V219" s="1"/>
       <c r="W219" s="1"/>
+      <c r="X219" s="1"/>
+      <c r="Y219" s="1"/>
     </row>
     <row r="220">
       <c r="A220" s="1"/>
@@ -9645,6 +10410,8 @@
       <c r="U220" s="1"/>
       <c r="V220" s="1"/>
       <c r="W220" s="1"/>
+      <c r="X220" s="1"/>
+      <c r="Y220" s="1"/>
     </row>
     <row r="221">
       <c r="A221" s="1"/>
@@ -9670,6 +10437,8 @@
       <c r="U221" s="1"/>
       <c r="V221" s="1"/>
       <c r="W221" s="1"/>
+      <c r="X221" s="1"/>
+      <c r="Y221" s="1"/>
     </row>
     <row r="222">
       <c r="A222" s="1"/>
@@ -9695,6 +10464,8 @@
       <c r="U222" s="1"/>
       <c r="V222" s="1"/>
       <c r="W222" s="1"/>
+      <c r="X222" s="1"/>
+      <c r="Y222" s="1"/>
     </row>
     <row r="223">
       <c r="A223" s="1"/>
@@ -9720,6 +10491,8 @@
       <c r="U223" s="1"/>
       <c r="V223" s="1"/>
       <c r="W223" s="1"/>
+      <c r="X223" s="1"/>
+      <c r="Y223" s="1"/>
     </row>
     <row r="224">
       <c r="A224" s="1"/>
@@ -9745,6 +10518,8 @@
       <c r="U224" s="1"/>
       <c r="V224" s="1"/>
       <c r="W224" s="1"/>
+      <c r="X224" s="1"/>
+      <c r="Y224" s="1"/>
     </row>
     <row r="225">
       <c r="A225" s="1"/>
@@ -9770,6 +10545,8 @@
       <c r="U225" s="1"/>
       <c r="V225" s="1"/>
       <c r="W225" s="1"/>
+      <c r="X225" s="1"/>
+      <c r="Y225" s="1"/>
     </row>
     <row r="226">
       <c r="A226" s="1"/>
@@ -9795,6 +10572,8 @@
       <c r="U226" s="1"/>
       <c r="V226" s="1"/>
       <c r="W226" s="1"/>
+      <c r="X226" s="1"/>
+      <c r="Y226" s="1"/>
     </row>
     <row r="227">
       <c r="A227" s="1"/>
@@ -9820,6 +10599,8 @@
       <c r="U227" s="1"/>
       <c r="V227" s="1"/>
       <c r="W227" s="1"/>
+      <c r="X227" s="1"/>
+      <c r="Y227" s="1"/>
     </row>
     <row r="228">
       <c r="A228" s="1"/>
@@ -9845,6 +10626,8 @@
       <c r="U228" s="1"/>
       <c r="V228" s="1"/>
       <c r="W228" s="1"/>
+      <c r="X228" s="1"/>
+      <c r="Y228" s="1"/>
     </row>
     <row r="229">
       <c r="A229" s="1"/>
@@ -9870,6 +10653,8 @@
       <c r="U229" s="1"/>
       <c r="V229" s="1"/>
       <c r="W229" s="1"/>
+      <c r="X229" s="1"/>
+      <c r="Y229" s="1"/>
     </row>
     <row r="230">
       <c r="A230" s="1"/>
@@ -9895,6 +10680,8 @@
       <c r="U230" s="1"/>
       <c r="V230" s="1"/>
       <c r="W230" s="1"/>
+      <c r="X230" s="1"/>
+      <c r="Y230" s="1"/>
     </row>
     <row r="231">
       <c r="A231" s="1"/>
@@ -9920,6 +10707,8 @@
       <c r="U231" s="1"/>
       <c r="V231" s="1"/>
       <c r="W231" s="1"/>
+      <c r="X231" s="1"/>
+      <c r="Y231" s="1"/>
     </row>
     <row r="232">
       <c r="A232" s="1"/>
@@ -9945,6 +10734,8 @@
       <c r="U232" s="1"/>
       <c r="V232" s="1"/>
       <c r="W232" s="1"/>
+      <c r="X232" s="1"/>
+      <c r="Y232" s="1"/>
     </row>
     <row r="233">
       <c r="A233" s="1"/>
@@ -9970,6 +10761,8 @@
       <c r="U233" s="1"/>
       <c r="V233" s="1"/>
       <c r="W233" s="1"/>
+      <c r="X233" s="1"/>
+      <c r="Y233" s="1"/>
     </row>
     <row r="234">
       <c r="A234" s="1"/>
@@ -9995,6 +10788,8 @@
       <c r="U234" s="1"/>
       <c r="V234" s="1"/>
       <c r="W234" s="1"/>
+      <c r="X234" s="1"/>
+      <c r="Y234" s="1"/>
     </row>
     <row r="235">
       <c r="A235" s="1"/>
@@ -10020,6 +10815,8 @@
       <c r="U235" s="1"/>
       <c r="V235" s="1"/>
       <c r="W235" s="1"/>
+      <c r="X235" s="1"/>
+      <c r="Y235" s="1"/>
     </row>
     <row r="236">
       <c r="A236" s="1"/>
@@ -10045,6 +10842,8 @@
       <c r="U236" s="1"/>
       <c r="V236" s="1"/>
       <c r="W236" s="1"/>
+      <c r="X236" s="1"/>
+      <c r="Y236" s="1"/>
     </row>
     <row r="237">
       <c r="A237" s="1"/>
@@ -10070,6 +10869,8 @@
       <c r="U237" s="1"/>
       <c r="V237" s="1"/>
       <c r="W237" s="1"/>
+      <c r="X237" s="1"/>
+      <c r="Y237" s="1"/>
     </row>
     <row r="238">
       <c r="A238" s="1"/>
@@ -10095,6 +10896,8 @@
       <c r="U238" s="1"/>
       <c r="V238" s="1"/>
       <c r="W238" s="1"/>
+      <c r="X238" s="1"/>
+      <c r="Y238" s="1"/>
     </row>
     <row r="239">
       <c r="A239" s="1"/>
@@ -10120,6 +10923,8 @@
       <c r="U239" s="1"/>
       <c r="V239" s="1"/>
       <c r="W239" s="1"/>
+      <c r="X239" s="1"/>
+      <c r="Y239" s="1"/>
     </row>
     <row r="240">
       <c r="A240" s="1"/>
@@ -10145,6 +10950,8 @@
       <c r="U240" s="1"/>
       <c r="V240" s="1"/>
       <c r="W240" s="1"/>
+      <c r="X240" s="1"/>
+      <c r="Y240" s="1"/>
     </row>
     <row r="241">
       <c r="A241" s="1"/>
@@ -10170,6 +10977,8 @@
       <c r="U241" s="1"/>
       <c r="V241" s="1"/>
       <c r="W241" s="1"/>
+      <c r="X241" s="1"/>
+      <c r="Y241" s="1"/>
     </row>
     <row r="242">
       <c r="A242" s="1"/>
@@ -10195,6 +11004,8 @@
       <c r="U242" s="1"/>
       <c r="V242" s="1"/>
       <c r="W242" s="1"/>
+      <c r="X242" s="1"/>
+      <c r="Y242" s="1"/>
     </row>
     <row r="243">
       <c r="A243" s="1"/>
@@ -10220,6 +11031,8 @@
       <c r="U243" s="1"/>
       <c r="V243" s="1"/>
       <c r="W243" s="1"/>
+      <c r="X243" s="1"/>
+      <c r="Y243" s="1"/>
     </row>
     <row r="244">
       <c r="A244" s="1"/>
@@ -10245,6 +11058,8 @@
       <c r="U244" s="1"/>
       <c r="V244" s="1"/>
       <c r="W244" s="1"/>
+      <c r="X244" s="1"/>
+      <c r="Y244" s="1"/>
     </row>
     <row r="245">
       <c r="A245" s="1"/>
@@ -10270,6 +11085,8 @@
       <c r="U245" s="1"/>
       <c r="V245" s="1"/>
       <c r="W245" s="1"/>
+      <c r="X245" s="1"/>
+      <c r="Y245" s="1"/>
     </row>
     <row r="246">
       <c r="A246" s="1"/>
@@ -10295,6 +11112,8 @@
       <c r="U246" s="1"/>
       <c r="V246" s="1"/>
       <c r="W246" s="1"/>
+      <c r="X246" s="1"/>
+      <c r="Y246" s="1"/>
     </row>
     <row r="247">
       <c r="A247" s="1"/>
@@ -10320,6 +11139,8 @@
       <c r="U247" s="1"/>
       <c r="V247" s="1"/>
       <c r="W247" s="1"/>
+      <c r="X247" s="1"/>
+      <c r="Y247" s="1"/>
     </row>
     <row r="248">
       <c r="A248" s="1"/>
@@ -10345,6 +11166,8 @@
       <c r="U248" s="1"/>
       <c r="V248" s="1"/>
       <c r="W248" s="1"/>
+      <c r="X248" s="1"/>
+      <c r="Y248" s="1"/>
     </row>
     <row r="249">
       <c r="A249" s="1"/>
@@ -10370,6 +11193,8 @@
       <c r="U249" s="1"/>
       <c r="V249" s="1"/>
       <c r="W249" s="1"/>
+      <c r="X249" s="1"/>
+      <c r="Y249" s="1"/>
     </row>
     <row r="250">
       <c r="A250" s="1"/>
@@ -10395,6 +11220,8 @@
       <c r="U250" s="1"/>
       <c r="V250" s="1"/>
       <c r="W250" s="1"/>
+      <c r="X250" s="1"/>
+      <c r="Y250" s="1"/>
     </row>
     <row r="251">
       <c r="A251" s="1"/>
@@ -10420,6 +11247,8 @@
       <c r="U251" s="1"/>
       <c r="V251" s="1"/>
       <c r="W251" s="1"/>
+      <c r="X251" s="1"/>
+      <c r="Y251" s="1"/>
     </row>
     <row r="252">
       <c r="A252" s="1"/>
@@ -10445,6 +11274,8 @@
       <c r="U252" s="1"/>
       <c r="V252" s="1"/>
       <c r="W252" s="1"/>
+      <c r="X252" s="1"/>
+      <c r="Y252" s="1"/>
     </row>
     <row r="253">
       <c r="A253" s="1"/>
@@ -10470,6 +11301,8 @@
       <c r="U253" s="1"/>
       <c r="V253" s="1"/>
       <c r="W253" s="1"/>
+      <c r="X253" s="1"/>
+      <c r="Y253" s="1"/>
     </row>
     <row r="254">
       <c r="A254" s="1"/>
@@ -10495,6 +11328,8 @@
       <c r="U254" s="1"/>
       <c r="V254" s="1"/>
       <c r="W254" s="1"/>
+      <c r="X254" s="1"/>
+      <c r="Y254" s="1"/>
     </row>
     <row r="255">
       <c r="A255" s="1"/>
@@ -10520,6 +11355,8 @@
       <c r="U255" s="1"/>
       <c r="V255" s="1"/>
       <c r="W255" s="1"/>
+      <c r="X255" s="1"/>
+      <c r="Y255" s="1"/>
     </row>
     <row r="256">
       <c r="A256" s="1"/>
@@ -10545,6 +11382,8 @@
       <c r="U256" s="1"/>
       <c r="V256" s="1"/>
       <c r="W256" s="1"/>
+      <c r="X256" s="1"/>
+      <c r="Y256" s="1"/>
     </row>
     <row r="257">
       <c r="A257" s="1"/>
@@ -10570,6 +11409,8 @@
       <c r="U257" s="1"/>
       <c r="V257" s="1"/>
       <c r="W257" s="1"/>
+      <c r="X257" s="1"/>
+      <c r="Y257" s="1"/>
     </row>
     <row r="258">
       <c r="A258" s="1"/>
@@ -10595,6 +11436,8 @@
       <c r="U258" s="1"/>
       <c r="V258" s="1"/>
       <c r="W258" s="1"/>
+      <c r="X258" s="1"/>
+      <c r="Y258" s="1"/>
     </row>
     <row r="259">
       <c r="A259" s="1"/>
@@ -10620,6 +11463,8 @@
       <c r="U259" s="1"/>
       <c r="V259" s="1"/>
       <c r="W259" s="1"/>
+      <c r="X259" s="1"/>
+      <c r="Y259" s="1"/>
     </row>
     <row r="260">
       <c r="A260" s="1"/>
@@ -10645,6 +11490,8 @@
       <c r="U260" s="1"/>
       <c r="V260" s="1"/>
       <c r="W260" s="1"/>
+      <c r="X260" s="1"/>
+      <c r="Y260" s="1"/>
     </row>
     <row r="261">
       <c r="A261" s="1"/>
@@ -10670,6 +11517,8 @@
       <c r="U261" s="1"/>
       <c r="V261" s="1"/>
       <c r="W261" s="1"/>
+      <c r="X261" s="1"/>
+      <c r="Y261" s="1"/>
     </row>
     <row r="262">
       <c r="A262" s="1"/>
@@ -10695,6 +11544,8 @@
       <c r="U262" s="1"/>
       <c r="V262" s="1"/>
       <c r="W262" s="1"/>
+      <c r="X262" s="1"/>
+      <c r="Y262" s="1"/>
     </row>
     <row r="263">
       <c r="A263" s="1"/>
@@ -10720,6 +11571,8 @@
       <c r="U263" s="1"/>
       <c r="V263" s="1"/>
       <c r="W263" s="1"/>
+      <c r="X263" s="1"/>
+      <c r="Y263" s="1"/>
     </row>
     <row r="264">
       <c r="A264" s="1"/>
@@ -10745,6 +11598,8 @@
       <c r="U264" s="1"/>
       <c r="V264" s="1"/>
       <c r="W264" s="1"/>
+      <c r="X264" s="1"/>
+      <c r="Y264" s="1"/>
     </row>
     <row r="265">
       <c r="A265" s="1"/>
@@ -10770,6 +11625,8 @@
       <c r="U265" s="1"/>
       <c r="V265" s="1"/>
       <c r="W265" s="1"/>
+      <c r="X265" s="1"/>
+      <c r="Y265" s="1"/>
     </row>
     <row r="266">
       <c r="A266" s="1"/>
@@ -10795,6 +11652,8 @@
       <c r="U266" s="1"/>
       <c r="V266" s="1"/>
       <c r="W266" s="1"/>
+      <c r="X266" s="1"/>
+      <c r="Y266" s="1"/>
     </row>
     <row r="267">
       <c r="A267" s="1"/>
@@ -10820,6 +11679,8 @@
       <c r="U267" s="1"/>
       <c r="V267" s="1"/>
       <c r="W267" s="1"/>
+      <c r="X267" s="1"/>
+      <c r="Y267" s="1"/>
     </row>
     <row r="268">
       <c r="A268" s="1"/>
@@ -10845,6 +11706,8 @@
       <c r="U268" s="1"/>
       <c r="V268" s="1"/>
       <c r="W268" s="1"/>
+      <c r="X268" s="1"/>
+      <c r="Y268" s="1"/>
     </row>
     <row r="269">
       <c r="A269" s="1"/>
@@ -10870,6 +11733,8 @@
       <c r="U269" s="1"/>
       <c r="V269" s="1"/>
       <c r="W269" s="1"/>
+      <c r="X269" s="1"/>
+      <c r="Y269" s="1"/>
     </row>
     <row r="270">
       <c r="A270" s="1"/>
@@ -10895,6 +11760,8 @@
       <c r="U270" s="1"/>
       <c r="V270" s="1"/>
       <c r="W270" s="1"/>
+      <c r="X270" s="1"/>
+      <c r="Y270" s="1"/>
     </row>
     <row r="271">
       <c r="A271" s="1"/>
@@ -10920,6 +11787,8 @@
       <c r="U271" s="1"/>
       <c r="V271" s="1"/>
       <c r="W271" s="1"/>
+      <c r="X271" s="1"/>
+      <c r="Y271" s="1"/>
     </row>
     <row r="272">
       <c r="A272" s="1"/>
@@ -10945,6 +11814,8 @@
       <c r="U272" s="1"/>
       <c r="V272" s="1"/>
       <c r="W272" s="1"/>
+      <c r="X272" s="1"/>
+      <c r="Y272" s="1"/>
     </row>
     <row r="273">
       <c r="A273" s="1"/>
@@ -10970,6 +11841,8 @@
       <c r="U273" s="1"/>
       <c r="V273" s="1"/>
       <c r="W273" s="1"/>
+      <c r="X273" s="1"/>
+      <c r="Y273" s="1"/>
     </row>
     <row r="274">
       <c r="A274" s="1"/>
@@ -10995,6 +11868,8 @@
       <c r="U274" s="1"/>
       <c r="V274" s="1"/>
       <c r="W274" s="1"/>
+      <c r="X274" s="1"/>
+      <c r="Y274" s="1"/>
     </row>
     <row r="275">
       <c r="A275" s="1"/>
@@ -11020,6 +11895,8 @@
       <c r="U275" s="1"/>
       <c r="V275" s="1"/>
       <c r="W275" s="1"/>
+      <c r="X275" s="1"/>
+      <c r="Y275" s="1"/>
     </row>
     <row r="276">
       <c r="A276" s="1"/>
@@ -11045,6 +11922,8 @@
       <c r="U276" s="1"/>
       <c r="V276" s="1"/>
       <c r="W276" s="1"/>
+      <c r="X276" s="1"/>
+      <c r="Y276" s="1"/>
     </row>
     <row r="277">
       <c r="A277" s="1"/>
@@ -11070,6 +11949,8 @@
       <c r="U277" s="1"/>
       <c r="V277" s="1"/>
       <c r="W277" s="1"/>
+      <c r="X277" s="1"/>
+      <c r="Y277" s="1"/>
     </row>
     <row r="278">
       <c r="A278" s="1"/>
@@ -11095,6 +11976,8 @@
       <c r="U278" s="1"/>
       <c r="V278" s="1"/>
       <c r="W278" s="1"/>
+      <c r="X278" s="1"/>
+      <c r="Y278" s="1"/>
     </row>
     <row r="279">
       <c r="A279" s="1"/>
@@ -11120,9 +12003,11 @@
       <c r="U279" s="1"/>
       <c r="V279" s="1"/>
       <c r="W279" s="1"/>
+      <c r="X279" s="1"/>
+      <c r="Y279" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W79"/>
+  <autoFilter ref="A1:Y79"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
